--- a/jogos_2025-07-04.xlsx
+++ b/jogos_2025-07-04.xlsx
@@ -241,21 +241,21 @@
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Estonia Meistriliiga</t>
   </si>
   <si>
+    <t>Republic of Ireland Premier Division</t>
+  </si>
+  <si>
     <t>Republic of Ireland First Division</t>
   </si>
   <si>
-    <t>Republic of Ireland Premier Division</t>
-  </si>
-  <si>
     <t>Paraguay Division Profesional</t>
   </si>
   <si>
@@ -280,18 +280,18 @@
     <t>Torpedo BelAZ</t>
   </si>
   <si>
+    <t>Sogdiana</t>
+  </si>
+  <si>
     <t>Termez Surkhon</t>
   </si>
   <si>
-    <t>Sogdiana</t>
+    <t>Kairat</t>
   </si>
   <si>
     <t>Oulu</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Dinamo Brest</t>
   </si>
   <si>
@@ -301,33 +301,33 @@
     <t>Neman Grodno</t>
   </si>
   <si>
+    <t>Derry City</t>
+  </si>
+  <si>
+    <t>Bray Wanderers</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
     <t>Kerry</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Derry City</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
@@ -346,12 +346,12 @@
     <t>FC Dallas</t>
   </si>
   <si>
+    <t>El Paso Locomotive</t>
+  </si>
+  <si>
     <t>Colorado Springs</t>
   </si>
   <si>
-    <t>El Paso Locomotive</t>
-  </si>
-  <si>
     <t>Colorado Rapids</t>
   </si>
   <si>
@@ -370,18 +370,18 @@
     <t>Molodechno-DYuSSh 4</t>
   </si>
   <si>
+    <t>Kokand-1912</t>
+  </si>
+  <si>
     <t>Buxoro</t>
   </si>
   <si>
-    <t>Kokand-1912</t>
+    <t>Turan Turkistan</t>
   </si>
   <si>
     <t>KuPS</t>
   </si>
   <si>
-    <t>Turan Turkistan</t>
-  </si>
-  <si>
     <t>Slutsk</t>
   </si>
   <si>
@@ -391,33 +391,33 @@
     <t>Isloch</t>
   </si>
   <si>
+    <t>Waterford</t>
+  </si>
+  <si>
+    <t>Wexford</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
     <t>Dundalk</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Waterford</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
     <t>Sportivo Trinidense</t>
   </si>
   <si>
@@ -436,10 +436,10 @@
     <t>Minnesota United</t>
   </si>
   <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
     <t>Louisville City</t>
-  </si>
-  <si>
-    <t>San Antonio</t>
   </si>
   <si>
     <t>Sporting KC</t>
@@ -1029,22 +1029,22 @@
         <v>146</v>
       </c>
       <c r="L2">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="M2">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N2">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R2">
         <v>1.29</v>
@@ -1053,13 +1053,13 @@
         <v>3.3</v>
       </c>
       <c r="T2">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U2">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V2">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="W2">
         <v>1.13</v>
@@ -1071,10 +1071,10 @@
         <v>13.5</v>
       </c>
       <c r="Z2">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AA2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB2">
         <v>1.55</v>
@@ -1083,10 +1083,10 @@
         <v>2.28</v>
       </c>
       <c r="AD2">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AE2">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF2">
         <v>1.5</v>
@@ -1110,7 +1110,7 @@
         <v>1.25</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN2">
         <v>1.44</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD2" s="3">
         <v>45842.27083333334</v>
@@ -1709,76 +1709,76 @@
         <v>146</v>
       </c>
       <c r="L6">
-        <v>3.77</v>
+        <v>1.12</v>
       </c>
       <c r="M6">
-        <v>3.37</v>
+        <v>6.2</v>
       </c>
       <c r="N6">
-        <v>1.79</v>
+        <v>17</v>
       </c>
       <c r="O6">
-        <v>2.45</v>
+        <v>1.1</v>
       </c>
       <c r="P6">
-        <v>11</v>
+        <v>15.75</v>
       </c>
       <c r="Q6">
-        <v>1.62</v>
+        <v>6.9</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S6">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V6">
-        <v>6.65</v>
+        <v>5.5</v>
       </c>
       <c r="W6">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>10.5</v>
+        <v>13.4</v>
       </c>
       <c r="Z6">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AA6">
         <v>4</v>
       </c>
       <c r="AB6">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AD6">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AE6">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AF6">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="AG6">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="AH6">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AI6">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AJ6" t="s">
         <v>147</v>
@@ -1787,13 +1787,13 @@
         <v>147</v>
       </c>
       <c r="AL6">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="AM6">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AN6">
-        <v>1.22</v>
+        <v>4.75</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1835,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>2.45</v>
+        <v>1.1</v>
       </c>
       <c r="BC6">
-        <v>1.62</v>
+        <v>6.9</v>
       </c>
       <c r="BD6" s="3">
         <v>45842.5</v>
@@ -1879,76 +1879,76 @@
         <v>146</v>
       </c>
       <c r="L7">
-        <v>1.14</v>
+        <v>3.77</v>
       </c>
       <c r="M7">
-        <v>6</v>
+        <v>3.37</v>
       </c>
       <c r="N7">
-        <v>15</v>
+        <v>1.79</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="R7">
         <v>1.3</v>
       </c>
       <c r="S7">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="T7">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="U7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V7">
+        <v>5.8</v>
+      </c>
+      <c r="W7">
+        <v>1.05</v>
+      </c>
+      <c r="X7">
+        <v>1.04</v>
+      </c>
+      <c r="Y7">
+        <v>12</v>
+      </c>
+      <c r="Z7">
+        <v>1.22</v>
+      </c>
+      <c r="AA7">
+        <v>3.9</v>
+      </c>
+      <c r="AB7">
+        <v>1.77</v>
+      </c>
+      <c r="AC7">
+        <v>1.93</v>
+      </c>
+      <c r="AD7">
+        <v>2.9</v>
+      </c>
+      <c r="AE7">
+        <v>1.36</v>
+      </c>
+      <c r="AF7">
+        <v>1.67</v>
+      </c>
+      <c r="AG7">
+        <v>2.1</v>
+      </c>
+      <c r="AH7">
         <v>5.5</v>
       </c>
-      <c r="W7">
-        <v>1.11</v>
-      </c>
-      <c r="X7">
-        <v>1.01</v>
-      </c>
-      <c r="Y7">
-        <v>11</v>
-      </c>
-      <c r="Z7">
-        <v>1.15</v>
-      </c>
-      <c r="AA7">
-        <v>4</v>
-      </c>
-      <c r="AB7">
-        <v>1.72</v>
-      </c>
-      <c r="AC7">
-        <v>2.07</v>
-      </c>
-      <c r="AD7">
-        <v>2.6</v>
-      </c>
-      <c r="AE7">
-        <v>1.44</v>
-      </c>
-      <c r="AF7">
-        <v>2.62</v>
-      </c>
-      <c r="AG7">
-        <v>1.42</v>
-      </c>
-      <c r="AH7">
-        <v>4.5</v>
-      </c>
       <c r="AI7">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AJ7" t="s">
         <v>147</v>
@@ -1957,13 +1957,13 @@
         <v>147</v>
       </c>
       <c r="AL7">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN7">
-        <v>4.75</v>
+        <v>1.22</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -2005,10 +2005,10 @@
         <v>0</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD7" s="3">
         <v>45842.5</v>
@@ -2228,43 +2228,43 @@
         <v>1.88</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB9">
         <v>1.65</v>
@@ -2273,22 +2273,22 @@
         <v>2</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ9" t="s">
         <v>147</v>
@@ -2297,13 +2297,13 @@
         <v>147</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2345,10 +2345,10 @@
         <v>0</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD9" s="3">
         <v>45842.54166666666</v>
@@ -2559,52 +2559,52 @@
         <v>146</v>
       </c>
       <c r="L11">
-        <v>4.6</v>
+        <v>1.52</v>
       </c>
       <c r="M11">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="N11">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="O11">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q11">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="R11">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S11">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="T11">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U11">
         <v>1.4</v>
       </c>
       <c r="V11">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="W11">
         <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z11">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="AA11">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AB11">
         <v>1.91</v>
@@ -2613,22 +2613,22 @@
         <v>1.79</v>
       </c>
       <c r="AD11">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="AE11">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AH11">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI11">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AJ11" t="s">
         <v>147</v>
@@ -2637,46 +2637,46 @@
         <v>147</v>
       </c>
       <c r="AL11">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN11">
-        <v>1.17</v>
+        <v>2.38</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ11">
         <v>0</v>
@@ -2685,10 +2685,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>3</v>
+        <v>1.4</v>
       </c>
       <c r="BC11">
-        <v>1.44</v>
+        <v>3.4</v>
       </c>
       <c r="BD11" s="3">
         <v>45842.65625</v>
@@ -2702,7 +2702,7 @@
         <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
         <v>85</v>
@@ -2753,13 +2753,13 @@
         <v>3.1</v>
       </c>
       <c r="T12">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="U12">
         <v>1.5</v>
       </c>
       <c r="V12">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="W12">
         <v>1.12</v>
@@ -2768,10 +2768,10 @@
         <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>13</v>
+        <v>11.8</v>
       </c>
       <c r="Z12">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA12">
         <v>4.2</v>
@@ -2783,22 +2783,22 @@
         <v>2.12</v>
       </c>
       <c r="AD12">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AE12">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF12">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
         <v>2.25</v>
       </c>
       <c r="AH12">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="AI12">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AJ12" t="s">
         <v>147</v>
@@ -2872,7 +2872,7 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>85</v>
@@ -2899,76 +2899,76 @@
         <v>146</v>
       </c>
       <c r="L13">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="M13">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="N13">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="O13">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P13">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R13">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="T13">
-        <v>2.65</v>
+        <v>2.44</v>
       </c>
       <c r="U13">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="W13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>10</v>
       </c>
       <c r="Z13">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AA13">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AB13">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD13">
-        <v>3.3</v>
+        <v>2.55</v>
       </c>
       <c r="AE13">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG13">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH13">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AI13">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AJ13" t="s">
         <v>147</v>
@@ -2983,7 +2983,7 @@
         <v>1.25</v>
       </c>
       <c r="AN13">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AO13">
         <v>-1</v>
@@ -3025,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BC13">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD13" s="3">
         <v>45842.65625</v>
@@ -3042,7 +3042,7 @@
         <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
         <v>85</v>
@@ -3069,76 +3069,76 @@
         <v>146</v>
       </c>
       <c r="L14">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="M14">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="N14">
-        <v>3.03</v>
+        <v>2.55</v>
       </c>
       <c r="O14">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="P14">
+        <v>7.5</v>
+      </c>
+      <c r="Q14">
+        <v>2.1</v>
+      </c>
+      <c r="R14">
+        <v>1.44</v>
+      </c>
+      <c r="S14">
+        <v>2.3</v>
+      </c>
+      <c r="T14">
+        <v>3.18</v>
+      </c>
+      <c r="U14">
+        <v>1.3</v>
+      </c>
+      <c r="V14">
         <v>8</v>
       </c>
-      <c r="Q14">
-        <v>2.25</v>
-      </c>
-      <c r="R14">
-        <v>1.42</v>
-      </c>
-      <c r="S14">
-        <v>2.5</v>
-      </c>
-      <c r="T14">
-        <v>3.08</v>
-      </c>
-      <c r="U14">
-        <v>1.33</v>
-      </c>
-      <c r="V14">
-        <v>7</v>
-      </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Z14">
         <v>1.36</v>
       </c>
       <c r="AA14">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC14">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AD14">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AE14">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF14">
         <v>1.85</v>
       </c>
       <c r="AG14">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH14">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="AI14">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="s">
         <v>147</v>
@@ -3147,46 +3147,46 @@
         <v>147</v>
       </c>
       <c r="AL14">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AM14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN14">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AQ14">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AR14">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AS14">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="AT14">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AU14">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="AV14">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AW14">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AX14">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AY14">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AZ14">
         <v>0</v>
@@ -3195,10 +3195,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="BC14">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="BD14" s="3">
         <v>45842.65625</v>
@@ -3239,76 +3239,76 @@
         <v>146</v>
       </c>
       <c r="L15">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="M15">
-        <v>3.18</v>
+        <v>3.62</v>
       </c>
       <c r="N15">
-        <v>2.91</v>
+        <v>5.3</v>
       </c>
       <c r="O15">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="P15">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S15">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="T15">
-        <v>2.49</v>
+        <v>2.93</v>
       </c>
       <c r="U15">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="V15">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="W15">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
+        <v>1.06</v>
+      </c>
+      <c r="Y15">
+        <v>8.6</v>
+      </c>
+      <c r="Z15">
+        <v>1.3</v>
+      </c>
+      <c r="AA15">
+        <v>3.2</v>
+      </c>
+      <c r="AB15">
+        <v>1.95</v>
+      </c>
+      <c r="AC15">
+        <v>1.7</v>
+      </c>
+      <c r="AD15">
+        <v>3.5</v>
+      </c>
+      <c r="AE15">
+        <v>1.23</v>
+      </c>
+      <c r="AF15">
+        <v>1.95</v>
+      </c>
+      <c r="AG15">
+        <v>1.73</v>
+      </c>
+      <c r="AH15">
+        <v>6.9</v>
+      </c>
+      <c r="AI15">
         <v>1.04</v>
-      </c>
-      <c r="Y15">
-        <v>12</v>
-      </c>
-      <c r="Z15">
-        <v>1.16</v>
-      </c>
-      <c r="AA15">
-        <v>4.2</v>
-      </c>
-      <c r="AB15">
-        <v>1.79</v>
-      </c>
-      <c r="AC15">
-        <v>1.91</v>
-      </c>
-      <c r="AD15">
-        <v>2.62</v>
-      </c>
-      <c r="AE15">
-        <v>1.4</v>
-      </c>
-      <c r="AF15">
-        <v>1.57</v>
-      </c>
-      <c r="AG15">
-        <v>2.3</v>
-      </c>
-      <c r="AH15">
-        <v>4.74</v>
-      </c>
-      <c r="AI15">
-        <v>1.15</v>
       </c>
       <c r="AJ15" t="s">
         <v>147</v>
@@ -3317,46 +3317,46 @@
         <v>147</v>
       </c>
       <c r="AL15">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AM15">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN15">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3365,10 +3365,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="BC15">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="BD15" s="3">
         <v>45842.65625</v>
@@ -3409,76 +3409,76 @@
         <v>146</v>
       </c>
       <c r="L16">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="M16">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="N16">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="O16">
+        <v>1.3</v>
+      </c>
+      <c r="P16">
+        <v>10</v>
+      </c>
+      <c r="Q16">
+        <v>3.75</v>
+      </c>
+      <c r="R16">
+        <v>1.35</v>
+      </c>
+      <c r="S16">
+        <v>2.8</v>
+      </c>
+      <c r="T16">
+        <v>2.35</v>
+      </c>
+      <c r="U16">
+        <v>1.5</v>
+      </c>
+      <c r="V16">
+        <v>5.6</v>
+      </c>
+      <c r="W16">
+        <v>1.12</v>
+      </c>
+      <c r="X16">
+        <v>1.01</v>
+      </c>
+      <c r="Y16">
+        <v>11</v>
+      </c>
+      <c r="Z16">
+        <v>1.2</v>
+      </c>
+      <c r="AA16">
+        <v>4.2</v>
+      </c>
+      <c r="AB16">
+        <v>1.6</v>
+      </c>
+      <c r="AC16">
+        <v>2.1</v>
+      </c>
+      <c r="AD16">
+        <v>2.7</v>
+      </c>
+      <c r="AE16">
         <v>1.4</v>
       </c>
-      <c r="P16">
-        <v>8.5</v>
-      </c>
-      <c r="Q16">
-        <v>3.5</v>
-      </c>
-      <c r="R16">
-        <v>1.42</v>
-      </c>
-      <c r="S16">
-        <v>2.65</v>
-      </c>
-      <c r="T16">
-        <v>2.8</v>
-      </c>
-      <c r="U16">
-        <v>1.37</v>
-      </c>
-      <c r="V16">
-        <v>7</v>
-      </c>
-      <c r="W16">
-        <v>1.07</v>
-      </c>
-      <c r="X16">
-        <v>1.03</v>
-      </c>
-      <c r="Y16">
-        <v>8.5</v>
-      </c>
-      <c r="Z16">
-        <v>1.31</v>
-      </c>
-      <c r="AA16">
-        <v>3.2</v>
-      </c>
-      <c r="AB16">
+      <c r="AF16">
+        <v>1.8</v>
+      </c>
+      <c r="AG16">
         <v>1.95</v>
       </c>
-      <c r="AC16">
-        <v>1.7</v>
-      </c>
-      <c r="AD16">
-        <v>3.55</v>
-      </c>
-      <c r="AE16">
-        <v>1.23</v>
-      </c>
-      <c r="AF16">
-        <v>1.95</v>
-      </c>
-      <c r="AG16">
-        <v>1.73</v>
-      </c>
       <c r="AH16">
-        <v>6.5</v>
+        <v>4.75</v>
       </c>
       <c r="AI16">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AJ16" t="s">
         <v>147</v>
@@ -3487,46 +3487,46 @@
         <v>147</v>
       </c>
       <c r="AL16">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AM16">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AN16">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3535,10 +3535,10 @@
         <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="BC16">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="BD16" s="3">
         <v>45842.65625</v>
@@ -3579,76 +3579,76 @@
         <v>146</v>
       </c>
       <c r="L17">
-        <v>1.52</v>
+        <v>2.2</v>
       </c>
       <c r="M17">
-        <v>3.7</v>
+        <v>3.33</v>
       </c>
       <c r="N17">
-        <v>5.3</v>
+        <v>2.74</v>
       </c>
       <c r="O17">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="P17">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q17">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="R17">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S17">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="T17">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U17">
         <v>1.4</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W17">
         <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Z17">
+        <v>1.29</v>
+      </c>
+      <c r="AA17">
+        <v>3.4</v>
+      </c>
+      <c r="AB17">
+        <v>1.85</v>
+      </c>
+      <c r="AC17">
+        <v>1.85</v>
+      </c>
+      <c r="AD17">
+        <v>3.2</v>
+      </c>
+      <c r="AE17">
         <v>1.3</v>
       </c>
-      <c r="AA17">
-        <v>3.25</v>
-      </c>
-      <c r="AB17">
-        <v>1.91</v>
-      </c>
-      <c r="AC17">
-        <v>1.79</v>
-      </c>
-      <c r="AD17">
-        <v>3.3</v>
-      </c>
-      <c r="AE17">
-        <v>1.28</v>
-      </c>
       <c r="AF17">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AH17">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AI17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AJ17" t="s">
         <v>147</v>
@@ -3657,46 +3657,46 @@
         <v>147</v>
       </c>
       <c r="AL17">
+        <v>1.33</v>
+      </c>
+      <c r="AM17">
         <v>1.25</v>
       </c>
-      <c r="AM17">
-        <v>1.2</v>
-      </c>
       <c r="AN17">
-        <v>2.25</v>
+        <v>1.49</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3705,10 +3705,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="BC17">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="BD17" s="3">
         <v>45842.65625</v>
@@ -3749,76 +3749,76 @@
         <v>146</v>
       </c>
       <c r="L18">
-        <v>1.38</v>
+        <v>2.14</v>
       </c>
       <c r="M18">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N18">
-        <v>6.2</v>
+        <v>3.03</v>
       </c>
       <c r="O18">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="P18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="R18">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="S18">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="T18">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="U18">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V18">
-        <v>5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W18">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.04</v>
       </c>
       <c r="Y18">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="Z18">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="AA18">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="AB18">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AC18">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="AD18">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="AE18">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF18">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AH18">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="AI18">
-        <v>1.17</v>
+        <v>1.02</v>
       </c>
       <c r="AJ18" t="s">
         <v>147</v>
@@ -3827,46 +3827,46 @@
         <v>147</v>
       </c>
       <c r="AL18">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AM18">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AN18">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU18">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW18">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AX18">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY18">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AZ18">
         <v>0</v>
@@ -3875,10 +3875,10 @@
         <v>0</v>
       </c>
       <c r="BB18">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="BC18">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="BD18" s="3">
         <v>45842.65625</v>
@@ -3919,76 +3919,76 @@
         <v>146</v>
       </c>
       <c r="L19">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="M19">
-        <v>3.03</v>
+        <v>3.56</v>
       </c>
       <c r="N19">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="O19">
+        <v>3</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>1.44</v>
+      </c>
+      <c r="R19">
+        <v>1.38</v>
+      </c>
+      <c r="S19">
+        <v>2.65</v>
+      </c>
+      <c r="T19">
+        <v>2.65</v>
+      </c>
+      <c r="U19">
+        <v>1.4</v>
+      </c>
+      <c r="V19">
+        <v>6.8</v>
+      </c>
+      <c r="W19">
+        <v>1.08</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>9.5</v>
+      </c>
+      <c r="Z19">
+        <v>1.3</v>
+      </c>
+      <c r="AA19">
+        <v>3.3</v>
+      </c>
+      <c r="AB19">
         <v>1.91</v>
       </c>
-      <c r="P19">
-        <v>7.5</v>
-      </c>
-      <c r="Q19">
-        <v>2.1</v>
-      </c>
-      <c r="R19">
-        <v>1.44</v>
-      </c>
-      <c r="S19">
-        <v>2.3</v>
-      </c>
-      <c r="T19">
-        <v>3.2</v>
-      </c>
-      <c r="U19">
-        <v>1.28</v>
-      </c>
-      <c r="V19">
-        <v>7.2</v>
-      </c>
-      <c r="W19">
-        <v>1.06</v>
-      </c>
-      <c r="X19">
-        <v>1.06</v>
-      </c>
-      <c r="Y19">
-        <v>7.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.36</v>
-      </c>
-      <c r="AA19">
-        <v>2.7</v>
-      </c>
-      <c r="AB19">
-        <v>2.15</v>
-      </c>
       <c r="AC19">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="AD19">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF19">
         <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH19">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="AI19">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AJ19" t="s">
         <v>147</v>
@@ -3997,46 +3997,46 @@
         <v>147</v>
       </c>
       <c r="AL19">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AM19">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AO19">
         <v>-1</v>
       </c>
       <c r="AP19">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ19">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR19">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS19">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT19">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AU19">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV19">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW19">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX19">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY19">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -4045,10 +4045,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="BC19">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="BD19" s="3">
         <v>45842.65625</v>
@@ -4289,10 +4289,10 @@
         <v>1.22</v>
       </c>
       <c r="V21">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
         <v>1.13</v>
@@ -4313,10 +4313,10 @@
         <v>1.36</v>
       </c>
       <c r="AD21">
-        <v>5.63</v>
+        <v>6</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF21">
         <v>2.4</v>
@@ -4328,7 +4328,7 @@
         <v>13</v>
       </c>
       <c r="AI21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ21" t="s">
         <v>147</v>
@@ -4429,76 +4429,76 @@
         <v>146</v>
       </c>
       <c r="L22">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="M22">
-        <v>3.09</v>
+        <v>3.3</v>
       </c>
       <c r="N22">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB22">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AC22">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ22" t="s">
         <v>147</v>
@@ -4507,13 +4507,13 @@
         <v>147</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO22">
         <v>-1</v>
@@ -4555,10 +4555,10 @@
         <v>0</v>
       </c>
       <c r="BB22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BC22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD22" s="3">
         <v>45842.83333333334</v>
@@ -4599,22 +4599,22 @@
         <v>146</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -4647,10 +4647,10 @@
         <v>0</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD23">
         <v>0</v>
@@ -4725,10 +4725,10 @@
         <v>0</v>
       </c>
       <c r="BB23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BD23" s="3">
         <v>45842.85416666666</v>
@@ -4769,22 +4769,22 @@
         <v>146</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -4817,10 +4817,10 @@
         <v>0</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD24">
         <v>0</v>
@@ -4895,10 +4895,10 @@
         <v>0</v>
       </c>
       <c r="BB24">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BC24">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD24" s="3">
         <v>45842.89583333334</v>
@@ -5109,13 +5109,13 @@
         <v>146</v>
       </c>
       <c r="L26">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="M26">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N26">
-        <v>1.81</v>
+        <v>3.05</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5127,58 +5127,58 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ26" t="s">
         <v>147</v>
@@ -5187,13 +5187,13 @@
         <v>147</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AM26">
         <v>0</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO26">
         <v>-1</v>
@@ -5279,76 +5279,76 @@
         <v>146</v>
       </c>
       <c r="L27">
-        <v>1.91</v>
+        <v>3.8</v>
       </c>
       <c r="M27">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="N27">
-        <v>2.87</v>
+        <v>1.81</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH27">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ27" t="s">
         <v>147</v>
@@ -5357,13 +5357,13 @@
         <v>147</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN27">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO27">
         <v>-1</v>
@@ -5405,10 +5405,10 @@
         <v>0</v>
       </c>
       <c r="BB27">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BC27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BD27" s="3">
         <v>45842.91666666666</v>
@@ -5628,67 +5628,67 @@
         <v>1.75</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AI29">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ29" t="s">
         <v>147</v>
@@ -5697,13 +5697,13 @@
         <v>147</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO29">
         <v>-1</v>
@@ -5745,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="BB29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BC29">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BD29" s="3">
         <v>45842.97916666666</v>
@@ -5798,67 +5798,67 @@
         <v>3.8</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AJ30" t="s">
         <v>147</v>
@@ -5867,13 +5867,13 @@
         <v>147</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO30">
         <v>-1</v>
@@ -5915,10 +5915,10 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD30" s="3">
         <v>45842.97916666666</v>

--- a/jogos_2025-07-04.xlsx
+++ b/jogos_2025-07-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="150">
   <si>
     <t>Date</t>
   </si>
@@ -238,12 +238,12 @@
     <t>Belarus Vysheyshaya Liga</t>
   </si>
   <si>
+    <t>Kazakhstan Kazakhstan Premier League</t>
+  </si>
+  <si>
     <t>Uzbekistan Uzbekistan Super League</t>
   </si>
   <si>
-    <t>Kazakhstan Kazakhstan Premier League</t>
-  </si>
-  <si>
     <t>Finland Veikkausliiga</t>
   </si>
   <si>
@@ -280,15 +280,15 @@
     <t>Torpedo BelAZ</t>
   </si>
   <si>
+    <t>Kairat</t>
+  </si>
+  <si>
     <t>Sogdiana</t>
   </si>
   <si>
     <t>Termez Surkhon</t>
   </si>
   <si>
-    <t>Kairat</t>
-  </si>
-  <si>
     <t>Oulu</t>
   </si>
   <si>
@@ -301,33 +301,33 @@
     <t>Neman Grodno</t>
   </si>
   <si>
+    <t>Drogheda United</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
     <t>Derry City</t>
   </si>
   <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>UCD</t>
+  </si>
+  <si>
     <t>Bray Wanderers</t>
   </si>
   <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
-    <t>Drogheda United</t>
-  </si>
-  <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>UCD</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Kerry</t>
-  </si>
-  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
@@ -355,30 +355,30 @@
     <t>Colorado Rapids</t>
   </si>
   <si>
+    <t>Phoenix Rising</t>
+  </si>
+  <si>
+    <t>LA Galaxy</t>
+  </si>
+  <si>
     <t>Las Vegas Lights</t>
   </si>
   <si>
-    <t>Phoenix Rising</t>
-  </si>
-  <si>
-    <t>LA Galaxy</t>
-  </si>
-  <si>
     <t>Sydney Olympic</t>
   </si>
   <si>
     <t>Molodechno-DYuSSh 4</t>
   </si>
   <si>
+    <t>Turan Turkistan</t>
+  </si>
+  <si>
     <t>Kokand-1912</t>
   </si>
   <si>
     <t>Buxoro</t>
   </si>
   <si>
-    <t>Turan Turkistan</t>
-  </si>
-  <si>
     <t>KuPS</t>
   </si>
   <si>
@@ -391,33 +391,33 @@
     <t>Isloch</t>
   </si>
   <si>
+    <t>Galway United</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
     <t>Waterford</t>
   </si>
   <si>
+    <t>Cork City</t>
+  </si>
+  <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Treaty United</t>
+  </si>
+  <si>
     <t>Wexford</t>
   </si>
   <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
-    <t>Galway United</t>
-  </si>
-  <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Treaty United</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Dundalk</t>
-  </si>
-  <si>
     <t>Sportivo Trinidense</t>
   </si>
   <si>
@@ -445,19 +445,25 @@
     <t>Sporting KC</t>
   </si>
   <si>
+    <t>Lexington</t>
+  </si>
+  <si>
+    <t>Vancouver Whitecaps</t>
+  </si>
+  <si>
     <t>Sacramento Republic</t>
   </si>
   <si>
-    <t>Lexington</t>
-  </si>
-  <si>
-    <t>Vancouver Whitecaps</t>
+    <t>complete</t>
   </si>
   <si>
     <t>incomplete</t>
   </si>
   <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['28', '90']</t>
   </si>
 </sst>
 </file>
@@ -1017,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
         <v>146</v>
@@ -1032,10 +1038,10 @@
         <v>2.75</v>
       </c>
       <c r="M2">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="N2">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
         <v>2.2</v>
@@ -1047,106 +1053,106 @@
         <v>1.67</v>
       </c>
       <c r="R2">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="U2">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="V2">
-        <v>4.95</v>
+        <v>4.05</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AA2">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AB2">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="AC2">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="AD2">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AE2">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AF2">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AG2">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AH2">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AI2">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AJ2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AL2">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM2">
         <v>1.2</v>
       </c>
       <c r="AN2">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1196,16 +1202,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L3">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="M3">
-        <v>5.95</v>
+        <v>6.2</v>
       </c>
       <c r="N3">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1253,10 +1259,10 @@
         <v>1.95</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF3">
         <v>0</v>
@@ -1271,10 +1277,10 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1366,127 +1372,127 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AO4">
         <v>-1</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1495,10 +1501,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="BD4" s="3">
         <v>45842.5</v>
@@ -1512,7 +1518,7 @@
         <v>58</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
         <v>85</v>
@@ -1536,94 +1542,94 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P5">
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>13.8</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AJ5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AM5">
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1665,10 +1671,10 @@
         <v>0</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BD5" s="3">
         <v>45842.5</v>
@@ -1706,94 +1712,94 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L6">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="M6">
-        <v>6.2</v>
+        <v>3.55</v>
       </c>
       <c r="N6">
-        <v>17</v>
+        <v>3.85</v>
       </c>
       <c r="O6">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="P6">
-        <v>15.75</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>6.9</v>
+        <v>2.75</v>
       </c>
       <c r="R6">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S6">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="T6">
-        <v>2.4</v>
+        <v>3.04</v>
       </c>
       <c r="U6">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="V6">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
+        <v>1.01</v>
+      </c>
+      <c r="Y6">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Z6">
+        <v>1.32</v>
+      </c>
+      <c r="AA6">
+        <v>3</v>
+      </c>
+      <c r="AB6">
+        <v>2.1</v>
+      </c>
+      <c r="AC6">
+        <v>1.61</v>
+      </c>
+      <c r="AD6">
+        <v>3.7</v>
+      </c>
+      <c r="AE6">
+        <v>1.22</v>
+      </c>
+      <c r="AF6">
+        <v>1.97</v>
+      </c>
+      <c r="AG6">
+        <v>1.78</v>
+      </c>
+      <c r="AH6">
+        <v>7.9</v>
+      </c>
+      <c r="AI6">
         <v>1.02</v>
       </c>
-      <c r="Y6">
-        <v>13.4</v>
-      </c>
-      <c r="Z6">
-        <v>1.16</v>
-      </c>
-      <c r="AA6">
-        <v>4</v>
-      </c>
-      <c r="AB6">
-        <v>1.72</v>
-      </c>
-      <c r="AC6">
-        <v>2.07</v>
-      </c>
-      <c r="AD6">
-        <v>2.56</v>
-      </c>
-      <c r="AE6">
-        <v>1.4</v>
-      </c>
-      <c r="AF6">
-        <v>2.62</v>
-      </c>
-      <c r="AG6">
-        <v>1.42</v>
-      </c>
-      <c r="AH6">
-        <v>4.75</v>
-      </c>
-      <c r="AI6">
-        <v>1.15</v>
-      </c>
       <c r="AJ6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL6">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="AM6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>4.75</v>
+        <v>1.6</v>
       </c>
       <c r="AO6">
         <v>-1</v>
@@ -1835,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>1.1</v>
+        <v>1.62</v>
       </c>
       <c r="BC6">
-        <v>6.9</v>
+        <v>2.75</v>
       </c>
       <c r="BD6" s="3">
         <v>45842.5</v>
@@ -1876,7 +1882,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L7">
         <v>3.77</v>
@@ -1897,31 +1903,31 @@
         <v>1.62</v>
       </c>
       <c r="R7">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="T7">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="U7">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V7">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z7">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AA7">
         <v>3.9</v>
@@ -1933,70 +1939,70 @@
         <v>1.93</v>
       </c>
       <c r="AD7">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AE7">
         <v>1.36</v>
       </c>
       <c r="AF7">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AG7">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH7">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AI7">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL7">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AM7">
         <v>1.25</v>
       </c>
       <c r="AN7">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AO7">
         <v>-1</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ7">
         <v>0</v>
@@ -2046,16 +2052,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L8">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="M8">
-        <v>4.28</v>
+        <v>4.6</v>
       </c>
       <c r="N8">
-        <v>5.95</v>
+        <v>7.5</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -2097,10 +2103,10 @@
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AC8">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -2121,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2216,7 +2222,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L9">
         <v>3.45</v>
@@ -2237,73 +2243,73 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="S9">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T9">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="U9">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="V9">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z9">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AA9">
-        <v>4.05</v>
+        <v>4.3</v>
       </c>
       <c r="AB9">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AC9">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AD9">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AE9">
         <v>1.42</v>
       </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="AH9">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="AI9">
         <v>1.15</v>
       </c>
       <c r="AJ9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL9">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AM9">
         <v>1.26</v>
       </c>
       <c r="AN9">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -2386,16 +2392,16 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L10">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="M10">
-        <v>3.58</v>
+        <v>3.21</v>
       </c>
       <c r="N10">
-        <v>5.45</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2437,10 +2443,10 @@
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC10">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2461,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2556,128 +2562,128 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11">
-        <v>1.52</v>
+        <v>2.52</v>
       </c>
       <c r="M11">
-        <v>3.7</v>
+        <v>3.03</v>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>2.55</v>
       </c>
       <c r="O11">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="P11">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q11">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="R11">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S11">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T11">
-        <v>2.7</v>
+        <v>3.13</v>
       </c>
       <c r="U11">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="V11">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="W11">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z11">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AA11">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AB11">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="AC11">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AD11">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AE11">
         <v>1.25</v>
       </c>
       <c r="AF11">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH11">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="AI11">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AJ11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL11">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="AM11">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AN11">
-        <v>2.38</v>
+        <v>1.47</v>
       </c>
       <c r="AO11">
         <v>-1</v>
       </c>
       <c r="AP11">
+        <v>1.29</v>
+      </c>
+      <c r="AQ11">
+        <v>1.48</v>
+      </c>
+      <c r="AR11">
+        <v>1.95</v>
+      </c>
+      <c r="AS11">
+        <v>2.18</v>
+      </c>
+      <c r="AT11">
+        <v>2.8</v>
+      </c>
+      <c r="AU11">
+        <v>3.3</v>
+      </c>
+      <c r="AV11">
+        <v>2.56</v>
+      </c>
+      <c r="AW11">
+        <v>1.99</v>
+      </c>
+      <c r="AX11">
+        <v>1.59</v>
+      </c>
+      <c r="AY11">
         <v>1.38</v>
       </c>
-      <c r="AQ11">
-        <v>1.65</v>
-      </c>
-      <c r="AR11">
-        <v>2.06</v>
-      </c>
-      <c r="AS11">
-        <v>2.65</v>
-      </c>
-      <c r="AT11">
-        <v>3.45</v>
-      </c>
-      <c r="AU11">
-        <v>2.7</v>
-      </c>
-      <c r="AV11">
-        <v>2.05</v>
-      </c>
-      <c r="AW11">
-        <v>1.65</v>
-      </c>
-      <c r="AX11">
-        <v>1.4</v>
-      </c>
-      <c r="AY11">
-        <v>1.25</v>
-      </c>
       <c r="AZ11">
         <v>0</v>
       </c>
@@ -2685,10 +2691,10 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="BC11">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="BD11" s="3">
         <v>45842.65625</v>
@@ -2726,127 +2732,127 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12">
+        <v>4.6</v>
+      </c>
+      <c r="M12">
+        <v>3.56</v>
+      </c>
+      <c r="N12">
+        <v>1.6</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>1.44</v>
+      </c>
+      <c r="R12">
+        <v>1.38</v>
+      </c>
+      <c r="S12">
+        <v>2.8</v>
+      </c>
+      <c r="T12">
+        <v>2.75</v>
+      </c>
+      <c r="U12">
+        <v>1.39</v>
+      </c>
+      <c r="V12">
+        <v>6.5</v>
+      </c>
+      <c r="W12">
+        <v>1.08</v>
+      </c>
+      <c r="X12">
+        <v>1.06</v>
+      </c>
+      <c r="Y12">
+        <v>9</v>
+      </c>
+      <c r="Z12">
+        <v>1.3</v>
+      </c>
+      <c r="AA12">
+        <v>3.2</v>
+      </c>
+      <c r="AB12">
+        <v>1.91</v>
+      </c>
+      <c r="AC12">
         <v>1.79</v>
       </c>
-      <c r="M12">
-        <v>3.5</v>
-      </c>
-      <c r="N12">
-        <v>3.63</v>
-      </c>
-      <c r="O12">
-        <v>1.57</v>
-      </c>
-      <c r="P12">
-        <v>9</v>
-      </c>
-      <c r="Q12">
-        <v>2.5</v>
-      </c>
-      <c r="R12">
-        <v>1.3</v>
-      </c>
-      <c r="S12">
-        <v>3.1</v>
-      </c>
-      <c r="T12">
-        <v>2.44</v>
-      </c>
-      <c r="U12">
-        <v>1.5</v>
-      </c>
-      <c r="V12">
-        <v>5.4</v>
-      </c>
-      <c r="W12">
-        <v>1.12</v>
-      </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>11.8</v>
-      </c>
-      <c r="Z12">
-        <v>1.18</v>
-      </c>
-      <c r="AA12">
-        <v>4.2</v>
-      </c>
-      <c r="AB12">
-        <v>1.64</v>
-      </c>
-      <c r="AC12">
-        <v>2.12</v>
-      </c>
       <c r="AD12">
-        <v>2.62</v>
+        <v>3.25</v>
       </c>
       <c r="AE12">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AF12">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AG12">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH12">
-        <v>4.8</v>
+        <v>6.25</v>
       </c>
       <c r="AI12">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AJ12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL12">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AM12">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AO12">
         <v>-1</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -2855,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.57</v>
+        <v>3</v>
       </c>
       <c r="BC12">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="BD12" s="3">
         <v>45842.65625</v>
@@ -2872,7 +2878,7 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
         <v>85</v>
@@ -2896,127 +2902,127 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L13">
-        <v>2.16</v>
+        <v>1.52</v>
       </c>
       <c r="M13">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="N13">
-        <v>2.91</v>
+        <v>5.3</v>
       </c>
       <c r="O13">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="P13">
+        <v>9.5</v>
+      </c>
+      <c r="Q13">
+        <v>3.4</v>
+      </c>
+      <c r="R13">
+        <v>1.38</v>
+      </c>
+      <c r="S13">
+        <v>2.8</v>
+      </c>
+      <c r="T13">
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <v>1.4</v>
+      </c>
+      <c r="V13">
+        <v>6.5</v>
+      </c>
+      <c r="W13">
+        <v>1.08</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
         <v>9</v>
       </c>
-      <c r="Q13">
-        <v>2.25</v>
-      </c>
-      <c r="R13">
+      <c r="Z13">
         <v>1.3</v>
       </c>
-      <c r="S13">
-        <v>3.1</v>
-      </c>
-      <c r="T13">
-        <v>2.44</v>
-      </c>
-      <c r="U13">
-        <v>1.5</v>
-      </c>
-      <c r="V13">
-        <v>5.4</v>
-      </c>
-      <c r="W13">
-        <v>1.12</v>
-      </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
-      <c r="Y13">
-        <v>10</v>
-      </c>
-      <c r="Z13">
-        <v>1.22</v>
-      </c>
       <c r="AA13">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AB13">
+        <v>1.91</v>
+      </c>
+      <c r="AC13">
         <v>1.79</v>
       </c>
-      <c r="AC13">
-        <v>1.91</v>
-      </c>
       <c r="AD13">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="AE13">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AF13">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AG13">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AH13">
-        <v>5.2</v>
+        <v>7.17</v>
       </c>
       <c r="AI13">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL13">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AM13">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AN13">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AO13">
         <v>-1</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ13">
         <v>0</v>
@@ -3025,10 +3031,10 @@
         <v>0</v>
       </c>
       <c r="BB13">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="BC13">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="BD13" s="3">
         <v>45842.65625</v>
@@ -3066,124 +3072,124 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L14">
-        <v>2.52</v>
+        <v>1.52</v>
       </c>
       <c r="M14">
-        <v>3.03</v>
+        <v>3.62</v>
       </c>
       <c r="N14">
-        <v>2.55</v>
+        <v>5.3</v>
       </c>
       <c r="O14">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="P14">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="R14">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S14">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="T14">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="U14">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
         <v>8.5</v>
       </c>
       <c r="Z14">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AA14">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AB14">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AD14">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="AE14">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF14">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG14">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AH14">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="AI14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AJ14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL14">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AM14">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AN14">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AR14">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AS14">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="AT14">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AU14">
-        <v>2.85</v>
+        <v>3.42</v>
       </c>
       <c r="AV14">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AW14">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AX14">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AY14">
         <v>1.28</v>
@@ -3195,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="BC14">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="BD14" s="3">
         <v>45842.65625</v>
@@ -3236,127 +3242,127 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L15">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="M15">
-        <v>3.62</v>
+        <v>3.1</v>
       </c>
       <c r="N15">
-        <v>5.3</v>
+        <v>3.03</v>
       </c>
       <c r="O15">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="P15">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
         <v>1.42</v>
       </c>
       <c r="S15">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="T15">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="U15">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V15">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="W15">
+        <v>1.06</v>
+      </c>
+      <c r="X15">
+        <v>1.05</v>
+      </c>
+      <c r="Y15">
+        <v>7.75</v>
+      </c>
+      <c r="Z15">
+        <v>1.33</v>
+      </c>
+      <c r="AA15">
+        <v>3</v>
+      </c>
+      <c r="AB15">
+        <v>2.05</v>
+      </c>
+      <c r="AC15">
+        <v>1.61</v>
+      </c>
+      <c r="AD15">
+        <v>3.6</v>
+      </c>
+      <c r="AE15">
+        <v>1.25</v>
+      </c>
+      <c r="AF15">
+        <v>1.88</v>
+      </c>
+      <c r="AG15">
+        <v>1.8</v>
+      </c>
+      <c r="AH15">
+        <v>7.8</v>
+      </c>
+      <c r="AI15">
         <v>1.07</v>
       </c>
-      <c r="X15">
-        <v>1.06</v>
-      </c>
-      <c r="Y15">
-        <v>8.6</v>
-      </c>
-      <c r="Z15">
-        <v>1.3</v>
-      </c>
-      <c r="AA15">
-        <v>3.2</v>
-      </c>
-      <c r="AB15">
-        <v>1.95</v>
-      </c>
-      <c r="AC15">
-        <v>1.7</v>
-      </c>
-      <c r="AD15">
-        <v>3.5</v>
-      </c>
-      <c r="AE15">
-        <v>1.23</v>
-      </c>
-      <c r="AF15">
-        <v>1.95</v>
-      </c>
-      <c r="AG15">
-        <v>1.73</v>
-      </c>
-      <c r="AH15">
-        <v>6.9</v>
-      </c>
-      <c r="AI15">
-        <v>1.04</v>
-      </c>
       <c r="AJ15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL15">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AM15">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AN15">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="AO15">
         <v>-1</v>
       </c>
       <c r="AP15">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AQ15">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="AR15">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AS15">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="AT15">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="AU15">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AV15">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AW15">
-        <v>1.62</v>
+        <v>2.09</v>
       </c>
       <c r="AX15">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AY15">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="AZ15">
         <v>0</v>
@@ -3365,10 +3371,10 @@
         <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="BC15">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="BD15" s="3">
         <v>45842.65625</v>
@@ -3406,7 +3412,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L16">
         <v>1.38</v>
@@ -3427,31 +3433,31 @@
         <v>3.75</v>
       </c>
       <c r="R16">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S16">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="T16">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="U16">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V16">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z16">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AA16">
         <v>4.2</v>
@@ -3463,70 +3469,70 @@
         <v>2.1</v>
       </c>
       <c r="AD16">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AE16">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF16">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG16">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AH16">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AI16">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AJ16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL16">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AM16">
         <v>1.15</v>
       </c>
       <c r="AN16">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AO16">
         <v>-1</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ16">
         <v>0</v>
@@ -3576,127 +3582,127 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L17">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="M17">
-        <v>3.33</v>
+        <v>3.18</v>
       </c>
       <c r="N17">
-        <v>2.74</v>
+        <v>2.91</v>
       </c>
       <c r="O17">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P17">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R17">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S17">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="T17">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="U17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V17">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>10</v>
       </c>
       <c r="Z17">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA17">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC17">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD17">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="AE17">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AF17">
         <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AI17">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AJ17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL17">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AM17">
         <v>1.25</v>
       </c>
       <c r="AN17">
-        <v>1.49</v>
+        <v>1.72</v>
       </c>
       <c r="AO17">
         <v>-1</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ17">
         <v>0</v>
@@ -3705,10 +3711,10 @@
         <v>0</v>
       </c>
       <c r="BB17">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BC17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" s="3">
         <v>45842.65625</v>
@@ -3722,7 +3728,7 @@
         <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D18" t="s">
         <v>85</v>
@@ -3746,139 +3752,139 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L18">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="M18">
+        <v>3.33</v>
+      </c>
+      <c r="N18">
+        <v>2.74</v>
+      </c>
+      <c r="O18">
+        <v>1.73</v>
+      </c>
+      <c r="P18">
+        <v>8.5</v>
+      </c>
+      <c r="Q18">
+        <v>2.2</v>
+      </c>
+      <c r="R18">
+        <v>1.4</v>
+      </c>
+      <c r="S18">
+        <v>2.8</v>
+      </c>
+      <c r="T18">
+        <v>2.8</v>
+      </c>
+      <c r="U18">
+        <v>1.4</v>
+      </c>
+      <c r="V18">
+        <v>7</v>
+      </c>
+      <c r="W18">
+        <v>1.08</v>
+      </c>
+      <c r="X18">
+        <v>1.01</v>
+      </c>
+      <c r="Y18">
+        <v>9.25</v>
+      </c>
+      <c r="Z18">
+        <v>1.29</v>
+      </c>
+      <c r="AA18">
+        <v>3.3</v>
+      </c>
+      <c r="AB18">
+        <v>1.85</v>
+      </c>
+      <c r="AC18">
+        <v>1.85</v>
+      </c>
+      <c r="AD18">
         <v>3.1</v>
       </c>
-      <c r="N18">
-        <v>3.03</v>
-      </c>
-      <c r="O18">
-        <v>1.8</v>
-      </c>
-      <c r="P18">
-        <v>8</v>
-      </c>
-      <c r="Q18">
-        <v>2.25</v>
-      </c>
-      <c r="R18">
-        <v>1.47</v>
-      </c>
-      <c r="S18">
-        <v>2.5</v>
-      </c>
-      <c r="T18">
-        <v>3.19</v>
-      </c>
-      <c r="U18">
-        <v>1.33</v>
-      </c>
-      <c r="V18">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="W18">
-        <v>1.07</v>
-      </c>
-      <c r="X18">
-        <v>1.04</v>
-      </c>
-      <c r="Y18">
-        <v>8.5</v>
-      </c>
-      <c r="Z18">
-        <v>1.36</v>
-      </c>
-      <c r="AA18">
-        <v>2.9</v>
-      </c>
-      <c r="AB18">
-        <v>2.05</v>
-      </c>
-      <c r="AC18">
-        <v>1.61</v>
-      </c>
-      <c r="AD18">
-        <v>3.85</v>
-      </c>
       <c r="AE18">
+        <v>1.32</v>
+      </c>
+      <c r="AF18">
+        <v>1.7</v>
+      </c>
+      <c r="AG18">
+        <v>2</v>
+      </c>
+      <c r="AH18">
+        <v>6.82</v>
+      </c>
+      <c r="AI18">
+        <v>1.1</v>
+      </c>
+      <c r="AJ18" t="s">
+        <v>148</v>
+      </c>
+      <c r="AK18" t="s">
+        <v>148</v>
+      </c>
+      <c r="AL18">
         <v>1.25</v>
       </c>
-      <c r="AF18">
-        <v>1.85</v>
-      </c>
-      <c r="AG18">
-        <v>1.83</v>
-      </c>
-      <c r="AH18">
-        <v>8</v>
-      </c>
-      <c r="AI18">
-        <v>1.02</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>147</v>
-      </c>
-      <c r="AK18" t="s">
-        <v>147</v>
-      </c>
-      <c r="AL18">
-        <v>1.33</v>
-      </c>
       <c r="AM18">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AO18">
         <v>-1</v>
       </c>
       <c r="AP18">
+        <v>1.35</v>
+      </c>
+      <c r="AQ18">
+        <v>1.68</v>
+      </c>
+      <c r="AR18">
+        <v>2.45</v>
+      </c>
+      <c r="AS18">
+        <v>2.73</v>
+      </c>
+      <c r="AT18">
+        <v>3.84</v>
+      </c>
+      <c r="AU18">
+        <v>2.81</v>
+      </c>
+      <c r="AV18">
+        <v>2.08</v>
+      </c>
+      <c r="AW18">
+        <v>1.66</v>
+      </c>
+      <c r="AX18">
+        <v>1.37</v>
+      </c>
+      <c r="AY18">
         <v>1.25</v>
       </c>
-      <c r="AQ18">
-        <v>1.44</v>
-      </c>
-      <c r="AR18">
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
         <v>1.73</v>
       </c>
-      <c r="AS18">
-        <v>2.14</v>
-      </c>
-      <c r="AT18">
-        <v>2.75</v>
-      </c>
-      <c r="AU18">
-        <v>3.4</v>
-      </c>
-      <c r="AV18">
-        <v>2.5</v>
-      </c>
-      <c r="AW18">
-        <v>1.95</v>
-      </c>
-      <c r="AX18">
-        <v>1.6</v>
-      </c>
-      <c r="AY18">
-        <v>1.37</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.8</v>
-      </c>
       <c r="BC18">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD18" s="3">
         <v>45842.65625</v>
@@ -3916,127 +3922,127 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L19">
-        <v>4.6</v>
+        <v>1.79</v>
       </c>
       <c r="M19">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="N19">
+        <v>3.63</v>
+      </c>
+      <c r="O19">
+        <v>1.57</v>
+      </c>
+      <c r="P19">
+        <v>9</v>
+      </c>
+      <c r="Q19">
+        <v>2.5</v>
+      </c>
+      <c r="R19">
+        <v>1.3</v>
+      </c>
+      <c r="S19">
+        <v>3.2</v>
+      </c>
+      <c r="T19">
+        <v>2.37</v>
+      </c>
+      <c r="U19">
+        <v>1.5</v>
+      </c>
+      <c r="V19">
+        <v>5.75</v>
+      </c>
+      <c r="W19">
+        <v>1.12</v>
+      </c>
+      <c r="X19">
+        <v>1.03</v>
+      </c>
+      <c r="Y19">
+        <v>11.5</v>
+      </c>
+      <c r="Z19">
+        <v>1.17</v>
+      </c>
+      <c r="AA19">
+        <v>4.2</v>
+      </c>
+      <c r="AB19">
+        <v>1.64</v>
+      </c>
+      <c r="AC19">
+        <v>2.12</v>
+      </c>
+      <c r="AD19">
+        <v>2.55</v>
+      </c>
+      <c r="AE19">
+        <v>1.44</v>
+      </c>
+      <c r="AF19">
         <v>1.6</v>
       </c>
-      <c r="O19">
-        <v>3</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>1.44</v>
-      </c>
-      <c r="R19">
-        <v>1.38</v>
-      </c>
-      <c r="S19">
-        <v>2.65</v>
-      </c>
-      <c r="T19">
-        <v>2.65</v>
-      </c>
-      <c r="U19">
-        <v>1.4</v>
-      </c>
-      <c r="V19">
-        <v>6.8</v>
-      </c>
-      <c r="W19">
-        <v>1.08</v>
-      </c>
-      <c r="X19">
-        <v>1.01</v>
-      </c>
-      <c r="Y19">
-        <v>9.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.3</v>
-      </c>
-      <c r="AA19">
-        <v>3.3</v>
-      </c>
-      <c r="AB19">
-        <v>1.91</v>
-      </c>
-      <c r="AC19">
-        <v>1.79</v>
-      </c>
-      <c r="AD19">
-        <v>3.4</v>
-      </c>
-      <c r="AE19">
-        <v>1.3</v>
-      </c>
-      <c r="AF19">
-        <v>1.85</v>
-      </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH19">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="AI19">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AJ19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL19">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN19">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO19">
         <v>-1</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ19">
         <v>0</v>
@@ -4045,10 +4051,10 @@
         <v>0</v>
       </c>
       <c r="BB19">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="BC19">
-        <v>1.44</v>
+        <v>2.5</v>
       </c>
       <c r="BD19" s="3">
         <v>45842.65625</v>
@@ -4086,16 +4092,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L20">
-        <v>3.22</v>
+        <v>3.02</v>
       </c>
       <c r="M20">
-        <v>3.22</v>
+        <v>3.06</v>
       </c>
       <c r="N20">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4161,10 +4167,10 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4256,7 +4262,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L21">
         <v>1.67</v>
@@ -4277,28 +4283,28 @@
         <v>3.25</v>
       </c>
       <c r="R21">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="S21">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="T21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Y21">
-        <v>5.75</v>
+        <v>7.5</v>
       </c>
       <c r="Z21">
         <v>1.6</v>
@@ -4307,58 +4313,58 @@
         <v>2.15</v>
       </c>
       <c r="AB21">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="AC21">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AE21">
         <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AG21">
         <v>1.44</v>
       </c>
       <c r="AH21">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AI21">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AJ21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL21">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AM21">
         <v>1.35</v>
       </c>
       <c r="AN21">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AO21">
         <v>-1</v>
       </c>
       <c r="AP21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AQ21">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AR21">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AS21">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AT21">
         <v>2.48</v>
@@ -4367,16 +4373,16 @@
         <v>3.8</v>
       </c>
       <c r="AV21">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AW21">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="AX21">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AY21">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AZ21">
         <v>0</v>
@@ -4426,16 +4432,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L22">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="M22">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="N22">
-        <v>2.65</v>
+        <v>3.38</v>
       </c>
       <c r="O22">
         <v>1.8</v>
@@ -4447,106 +4453,106 @@
         <v>2.1</v>
       </c>
       <c r="R22">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S22">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T22">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U22">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="V22">
         <v>7</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
+        <v>7</v>
+      </c>
+      <c r="Z22">
+        <v>1.4</v>
+      </c>
+      <c r="AA22">
+        <v>3</v>
+      </c>
+      <c r="AB22">
+        <v>2.2</v>
+      </c>
+      <c r="AC22">
+        <v>1.55</v>
+      </c>
+      <c r="AD22">
+        <v>3.55</v>
+      </c>
+      <c r="AE22">
+        <v>1.24</v>
+      </c>
+      <c r="AF22">
+        <v>2</v>
+      </c>
+      <c r="AG22">
+        <v>1.76</v>
+      </c>
+      <c r="AH22">
         <v>8</v>
-      </c>
-      <c r="Z22">
-        <v>1.36</v>
-      </c>
-      <c r="AA22">
-        <v>2.9</v>
-      </c>
-      <c r="AB22">
-        <v>1.86</v>
-      </c>
-      <c r="AC22">
-        <v>1.86</v>
-      </c>
-      <c r="AD22">
-        <v>3.95</v>
-      </c>
-      <c r="AE22">
-        <v>1.25</v>
-      </c>
-      <c r="AF22">
-        <v>1.7</v>
-      </c>
-      <c r="AG22">
-        <v>1.8</v>
-      </c>
-      <c r="AH22">
-        <v>7</v>
       </c>
       <c r="AI22">
         <v>1.07</v>
       </c>
       <c r="AJ22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK22" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL22">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AM22">
         <v>1.27</v>
       </c>
       <c r="AN22">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AO22">
         <v>-1</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS22">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AT22">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AU22">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AV22">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AW22">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AX22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AY22">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AZ22">
         <v>0</v>
@@ -4596,43 +4602,43 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L23">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M23">
-        <v>4.5</v>
+        <v>5.01</v>
       </c>
       <c r="N23">
-        <v>4.5</v>
+        <v>4.94</v>
       </c>
       <c r="O23">
         <v>1.36</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Q23">
         <v>3</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
         <v>0</v>
@@ -4641,49 +4647,49 @@
         <v>0</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB23">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AC23">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AJ23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AM23">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO23">
         <v>-1</v>
@@ -4766,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L24">
         <v>1.85</v>
@@ -4787,73 +4793,73 @@
         <v>2.4</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AB24">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AC24">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL24">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AM24">
         <v>0</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO24">
         <v>-1</v>
@@ -4936,7 +4942,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L25">
         <v>2.52</v>
@@ -4987,10 +4993,10 @@
         <v>4.61</v>
       </c>
       <c r="AB25">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AC25">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AD25">
         <v>2.62</v>
@@ -5011,10 +5017,10 @@
         <v>1.19</v>
       </c>
       <c r="AJ25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL25">
         <v>1.52</v>
@@ -5106,16 +5112,16 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="M26">
-        <v>3.55</v>
+        <v>3.39</v>
       </c>
       <c r="N26">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5127,106 +5133,106 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S26">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T26">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="U26">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="V26">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="W26">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
         <v>1</v>
       </c>
       <c r="Y26">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z26">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AA26">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="AB26">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AC26">
-        <v>2.19</v>
+        <v>1.87</v>
       </c>
       <c r="AD26">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AE26">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="AF26">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AH26">
-        <v>4.1</v>
+        <v>5.95</v>
       </c>
       <c r="AI26">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL26">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AM26">
         <v>0</v>
       </c>
       <c r="AN26">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AO26">
         <v>-1</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ26">
         <v>0</v>
@@ -5276,16 +5282,16 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L27">
-        <v>3.8</v>
+        <v>2.66</v>
       </c>
       <c r="M27">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="N27">
-        <v>1.81</v>
+        <v>2.24</v>
       </c>
       <c r="O27">
         <v>2.6</v>
@@ -5297,106 +5303,106 @@
         <v>1.53</v>
       </c>
       <c r="R27">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S27">
         <v>3.1</v>
       </c>
       <c r="T27">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="U27">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V27">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X27">
         <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AA27">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AB27">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AC27">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AD27">
-        <v>2.4</v>
+        <v>2.95</v>
       </c>
       <c r="AE27">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AF27">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AG27">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="AH27">
-        <v>4.33</v>
+        <v>5.5</v>
       </c>
       <c r="AI27">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AJ27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK27" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL27">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM27">
         <v>1.25</v>
       </c>
       <c r="AN27">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AO27">
         <v>-1</v>
       </c>
       <c r="AP27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AU27">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AV27">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW27">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AX27">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY27">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ27">
         <v>0</v>
@@ -5446,7 +5452,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L28">
         <v>1.82</v>
@@ -5497,16 +5503,16 @@
         <v>5.1</v>
       </c>
       <c r="AB28">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AC28">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD28">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AE28">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AF28">
         <v>1.53</v>
@@ -5521,10 +5527,10 @@
         <v>1.24</v>
       </c>
       <c r="AJ28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK28" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL28">
         <v>1.29</v>
@@ -5616,127 +5622,127 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L29">
-        <v>3.75</v>
+        <v>1.97</v>
       </c>
       <c r="M29">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N29">
+        <v>3.36</v>
+      </c>
+      <c r="O29">
+        <v>1.53</v>
+      </c>
+      <c r="P29">
+        <v>14</v>
+      </c>
+      <c r="Q29">
+        <v>2.5</v>
+      </c>
+      <c r="R29">
+        <v>1.38</v>
+      </c>
+      <c r="S29">
+        <v>2.85</v>
+      </c>
+      <c r="T29">
+        <v>2.65</v>
+      </c>
+      <c r="U29">
+        <v>1.39</v>
+      </c>
+      <c r="V29">
+        <v>6.75</v>
+      </c>
+      <c r="W29">
+        <v>1.08</v>
+      </c>
+      <c r="X29">
+        <v>1</v>
+      </c>
+      <c r="Y29">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Z29">
+        <v>1.37</v>
+      </c>
+      <c r="AA29">
+        <v>3.25</v>
+      </c>
+      <c r="AB29">
+        <v>1.9</v>
+      </c>
+      <c r="AC29">
+        <v>1.8</v>
+      </c>
+      <c r="AD29">
+        <v>3.4</v>
+      </c>
+      <c r="AE29">
+        <v>1.29</v>
+      </c>
+      <c r="AF29">
         <v>1.75</v>
       </c>
-      <c r="O29">
-        <v>2.5</v>
-      </c>
-      <c r="P29">
-        <v>15.75</v>
-      </c>
-      <c r="Q29">
-        <v>1.53</v>
-      </c>
-      <c r="R29">
-        <v>1.3</v>
-      </c>
-      <c r="S29">
-        <v>3.1</v>
-      </c>
-      <c r="T29">
-        <v>2.35</v>
-      </c>
-      <c r="U29">
-        <v>1.5</v>
-      </c>
-      <c r="V29">
-        <v>5</v>
-      </c>
-      <c r="W29">
-        <v>1.12</v>
-      </c>
-      <c r="X29">
-        <v>1.02</v>
-      </c>
-      <c r="Y29">
-        <v>10</v>
-      </c>
-      <c r="Z29">
-        <v>1.18</v>
-      </c>
-      <c r="AA29">
-        <v>4.2</v>
-      </c>
-      <c r="AB29">
-        <v>1.65</v>
-      </c>
-      <c r="AC29">
-        <v>2.12</v>
-      </c>
-      <c r="AD29">
-        <v>2.6</v>
-      </c>
-      <c r="AE29">
-        <v>1.42</v>
-      </c>
-      <c r="AF29">
-        <v>1.6</v>
-      </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AH29">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
       <c r="AI29">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="AJ29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL29">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AM29">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AN29">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="AO29">
         <v>-1</v>
       </c>
       <c r="AP29">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ29">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AT29">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AU29">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV29">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW29">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX29">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY29">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ29">
         <v>0</v>
@@ -5745,10 +5751,10 @@
         <v>0</v>
       </c>
       <c r="BB29">
+        <v>1.53</v>
+      </c>
+      <c r="BC29">
         <v>2.5</v>
-      </c>
-      <c r="BC29">
-        <v>1.53</v>
       </c>
       <c r="BD29" s="3">
         <v>45842.97916666666</v>
@@ -5762,7 +5768,7 @@
         <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
         <v>85</v>
@@ -5786,127 +5792,127 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L30">
-        <v>1.77</v>
+        <v>2.44</v>
       </c>
       <c r="M30">
-        <v>3.55</v>
+        <v>3.27</v>
       </c>
       <c r="N30">
-        <v>3.8</v>
+        <v>2.47</v>
       </c>
       <c r="O30">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="P30">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Q30">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="R30">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S30">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T30">
         <v>2.5</v>
       </c>
       <c r="U30">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V30">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="W30">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z30">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AA30">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AB30">
+        <v>1.66</v>
+      </c>
+      <c r="AC30">
+        <v>2.08</v>
+      </c>
+      <c r="AD30">
+        <v>2.15</v>
+      </c>
+      <c r="AE30">
         <v>1.61</v>
       </c>
-      <c r="AC30">
-        <v>2.19</v>
-      </c>
-      <c r="AD30">
-        <v>2.65</v>
-      </c>
-      <c r="AE30">
-        <v>1.42</v>
-      </c>
       <c r="AF30">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AG30">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH30">
         <v>4.6</v>
       </c>
       <c r="AI30">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AJ30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL30">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="AM30">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AN30">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AO30">
         <v>-1</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ30">
         <v>0</v>
@@ -5915,10 +5921,10 @@
         <v>0</v>
       </c>
       <c r="BB30">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="BC30">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="BD30" s="3">
         <v>45842.97916666666</v>
@@ -5932,7 +5938,7 @@
         <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
         <v>85</v>
@@ -5956,127 +5962,127 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L31">
-        <v>2.44</v>
+        <v>3.29</v>
       </c>
       <c r="M31">
-        <v>3.27</v>
+        <v>3.39</v>
       </c>
       <c r="N31">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="O31">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="P31">
-        <v>11</v>
+        <v>15.75</v>
       </c>
       <c r="Q31">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="R31">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S31">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="T31">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="U31">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="V31">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="W31">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="Z31">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AA31">
-        <v>4</v>
+        <v>3.11</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AC31">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD31">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="AE31">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="AF31">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AG31">
-        <v>2.38</v>
+        <v>1.88</v>
       </c>
       <c r="AH31">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="AI31">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AJ31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AK31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL31">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="AM31">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AN31">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="AO31">
         <v>-1</v>
       </c>
       <c r="AP31">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
       <c r="AQ31">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AR31">
-        <v>1.63</v>
+        <v>2.94</v>
       </c>
       <c r="AS31">
-        <v>1.98</v>
+        <v>3.28</v>
       </c>
       <c r="AT31">
-        <v>2.48</v>
+        <v>4.84</v>
       </c>
       <c r="AU31">
-        <v>3.8</v>
+        <v>2.41</v>
       </c>
       <c r="AV31">
-        <v>2.75</v>
+        <v>1.9</v>
       </c>
       <c r="AW31">
-        <v>2.12</v>
+        <v>1.49</v>
       </c>
       <c r="AX31">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="AY31">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="AZ31">
         <v>0</v>
@@ -6085,10 +6091,10 @@
         <v>0</v>
       </c>
       <c r="BB31">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="BC31">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="BD31" s="3">
         <v>45842.97916666666</v>

--- a/jogos_2025-07-04.xlsx
+++ b/jogos_2025-07-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="169">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -301,33 +247,33 @@
     <t>Neman Grodno</t>
   </si>
   <si>
+    <t>St Patrick's Athl.</t>
+  </si>
+  <si>
+    <t>Kerry</t>
+  </si>
+  <si>
+    <t>Cobh Ramblers</t>
+  </si>
+  <si>
+    <t>Finn Harps</t>
+  </si>
+  <si>
+    <t>Shelbourne</t>
+  </si>
+  <si>
     <t>Drogheda United</t>
   </si>
   <si>
-    <t>Kerry</t>
+    <t>Bray Wanderers</t>
   </si>
   <si>
     <t>Derry City</t>
   </si>
   <si>
-    <t>Shelbourne</t>
-  </si>
-  <si>
-    <t>St Patrick's Athl.</t>
-  </si>
-  <si>
-    <t>Cobh Ramblers</t>
-  </si>
-  <si>
-    <t>Finn Harps</t>
-  </si>
-  <si>
     <t>UCD</t>
   </si>
   <si>
-    <t>Bray Wanderers</t>
-  </si>
-  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
@@ -358,12 +304,12 @@
     <t>Phoenix Rising</t>
   </si>
   <si>
+    <t>Las Vegas Lights</t>
+  </si>
+  <si>
     <t>LA Galaxy</t>
   </si>
   <si>
-    <t>Las Vegas Lights</t>
-  </si>
-  <si>
     <t>Sydney Olympic</t>
   </si>
   <si>
@@ -391,33 +337,33 @@
     <t>Isloch</t>
   </si>
   <si>
+    <t>Bohemians</t>
+  </si>
+  <si>
+    <t>Dundalk</t>
+  </si>
+  <si>
+    <t>Athlone Town</t>
+  </si>
+  <si>
+    <t>Longford Town</t>
+  </si>
+  <si>
+    <t>Cork City</t>
+  </si>
+  <si>
     <t>Galway United</t>
   </si>
   <si>
-    <t>Dundalk</t>
+    <t>Wexford</t>
   </si>
   <si>
     <t>Waterford</t>
   </si>
   <si>
-    <t>Cork City</t>
-  </si>
-  <si>
-    <t>Bohemians</t>
-  </si>
-  <si>
-    <t>Athlone Town</t>
-  </si>
-  <si>
-    <t>Longford Town</t>
-  </si>
-  <si>
     <t>Treaty United</t>
   </si>
   <si>
-    <t>Wexford</t>
-  </si>
-  <si>
     <t>Sportivo Trinidense</t>
   </si>
   <si>
@@ -448,22 +394,133 @@
     <t>Lexington</t>
   </si>
   <si>
+    <t>Sacramento Republic</t>
+  </si>
+  <si>
     <t>Vancouver Whitecaps</t>
   </si>
   <si>
-    <t>Sacramento Republic</t>
-  </si>
-  <si>
     <t>complete</t>
   </si>
   <si>
-    <t>incomplete</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
+    <t>['7', '53', '87', '9003']</t>
+  </si>
+  <si>
+    <t>['84', '31', '39', '76']</t>
+  </si>
+  <si>
+    <t>['36', '41']</t>
+  </si>
+  <si>
+    <t>['78', '4']</t>
+  </si>
+  <si>
+    <t>['4', '39', '67']</t>
+  </si>
+  <si>
+    <t>['3', '89']</t>
+  </si>
+  <si>
+    <t>['5', '30']</t>
+  </si>
+  <si>
+    <t>['2', '6', '83']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['28']</t>
+  </si>
+  <si>
+    <t>['24', '5', '41', '36', '52', '57', '73']</t>
+  </si>
+  <si>
+    <t>['85']</t>
+  </si>
+  <si>
+    <t>['43', '76']</t>
+  </si>
+  <si>
+    <t>['18', '23']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['27']</t>
+  </si>
+  <si>
+    <t>['24', '6', '68', '75']</t>
+  </si>
+  <si>
+    <t>['67']</t>
+  </si>
+  <si>
+    <t>['89']</t>
+  </si>
+  <si>
+    <t>['2', '60', '77']</t>
+  </si>
+  <si>
     <t>['28', '90']</t>
+  </si>
+  <si>
+    <t>['23']</t>
+  </si>
+  <si>
+    <t>['47']</t>
+  </si>
+  <si>
+    <t>['65', '52']</t>
+  </si>
+  <si>
+    <t>['23', '59', '45+3']</t>
+  </si>
+  <si>
+    <t>['20', '60', '90+3', '90+4']</t>
+  </si>
+  <si>
+    <t>['81']</t>
+  </si>
+  <si>
+    <t>['42']</t>
+  </si>
+  <si>
+    <t>['49', '79']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['18', '23', '37', '28']</t>
+  </si>
+  <si>
+    <t>['84', '7']</t>
+  </si>
+  <si>
+    <t>['54']</t>
+  </si>
+  <si>
+    <t>['35', '58']</t>
+  </si>
+  <si>
+    <t>['11', '83']</t>
+  </si>
+  <si>
+    <t>['9']</t>
+  </si>
+  <si>
+    <t>['4', '53']</t>
+  </si>
+  <si>
+    <t>['34']</t>
+  </si>
+  <si>
+    <t>['50', '67']</t>
   </si>
 </sst>
 </file>
@@ -827,10 +884,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD31"/>
+  <dimension ref="A1:AL31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -945,79 +1002,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45842</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1032,7 +1035,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="L2">
         <v>2.75</v>
@@ -1107,102 +1110,48 @@
         <v>1.27</v>
       </c>
       <c r="AJ2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK2" t="s">
-        <v>149</v>
-      </c>
-      <c r="AL2">
-        <v>1.22</v>
-      </c>
-      <c r="AM2">
-        <v>1.2</v>
-      </c>
-      <c r="AN2">
-        <v>1.38</v>
-      </c>
-      <c r="AO2">
-        <v>10</v>
-      </c>
-      <c r="AP2">
-        <v>1.14</v>
-      </c>
-      <c r="AQ2">
-        <v>1.33</v>
-      </c>
-      <c r="AR2">
-        <v>1.61</v>
-      </c>
-      <c r="AS2">
-        <v>1.98</v>
-      </c>
-      <c r="AT2">
-        <v>2.53</v>
-      </c>
-      <c r="AU2">
-        <v>4.28</v>
-      </c>
-      <c r="AV2">
-        <v>2.89</v>
-      </c>
-      <c r="AW2">
-        <v>2.16</v>
-      </c>
-      <c r="AX2">
-        <v>1.74</v>
-      </c>
-      <c r="AY2">
-        <v>1.43</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>2.2</v>
-      </c>
-      <c r="BC2">
-        <v>1.67</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>150</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45842.27083333334</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45842</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="F3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L3">
         <v>1.16</v>
@@ -1277,111 +1226,57 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="AK3" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>-1</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>0</v>
-      </c>
-      <c r="BC3">
-        <v>0</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>151</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45842.4375</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45842</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L4">
-        <v>1.4</v>
+        <v>1.07</v>
       </c>
       <c r="M4">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="N4">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="O4">
         <v>1.1</v>
@@ -1396,7 +1291,7 @@
         <v>1.27</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="T4">
         <v>2.25</v>
@@ -1408,31 +1303,31 @@
         <v>4.75</v>
       </c>
       <c r="W4">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X4">
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Z4">
         <v>1.17</v>
       </c>
       <c r="AA4">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB4">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AC4">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD4">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AE4">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AF4">
         <v>2.5</v>
@@ -1444,114 +1339,60 @@
         <v>4</v>
       </c>
       <c r="AI4">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AJ4" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="AK4" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL4">
-        <v>1.01</v>
-      </c>
-      <c r="AM4">
-        <v>1.05</v>
-      </c>
-      <c r="AN4">
-        <v>4.75</v>
-      </c>
-      <c r="AO4">
-        <v>-1</v>
-      </c>
-      <c r="AP4">
-        <v>1.27</v>
-      </c>
-      <c r="AQ4">
-        <v>1.5</v>
-      </c>
-      <c r="AR4">
-        <v>1.83</v>
-      </c>
-      <c r="AS4">
-        <v>2.31</v>
-      </c>
-      <c r="AT4">
-        <v>2.92</v>
-      </c>
-      <c r="AU4">
-        <v>3.27</v>
-      </c>
-      <c r="AV4">
-        <v>2.26</v>
-      </c>
-      <c r="AW4">
-        <v>1.91</v>
-      </c>
-      <c r="AX4">
-        <v>1.57</v>
-      </c>
-      <c r="AY4">
-        <v>1.35</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.1</v>
-      </c>
-      <c r="BC4">
-        <v>6.9</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45842.5</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45842</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F5" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L5">
-        <v>1.61</v>
+        <v>1.42</v>
       </c>
       <c r="M5">
-        <v>3.65</v>
+        <v>4.83</v>
       </c>
       <c r="N5">
-        <v>4.9</v>
+        <v>6.83</v>
       </c>
       <c r="O5">
         <v>1.36</v>
@@ -1569,135 +1410,81 @@
         <v>3.09</v>
       </c>
       <c r="T5">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="U5">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="V5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W5">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
         <v>1</v>
       </c>
       <c r="Y5">
-        <v>13.8</v>
+        <v>13</v>
       </c>
       <c r="Z5">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AA5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AB5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AC5">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AD5">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AE5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG5">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="AH5">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AI5">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AJ5" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="AK5" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL5">
-        <v>1.18</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>2.6</v>
-      </c>
-      <c r="AO5">
-        <v>-1</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>0</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.36</v>
-      </c>
-      <c r="BC5">
-        <v>3.4</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>152</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45842.5</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45842</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1712,16 +1499,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L6">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="M6">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="N6">
-        <v>3.85</v>
+        <v>3.37</v>
       </c>
       <c r="O6">
         <v>1.62</v>
@@ -1739,159 +1526,105 @@
         <v>2.6</v>
       </c>
       <c r="T6">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V6">
         <v>8</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="Z6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AA6">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC6">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AD6">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AE6">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="AG6">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AH6">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AI6">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ6" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK6" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL6">
-        <v>1.24</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>1.6</v>
-      </c>
-      <c r="AO6">
-        <v>-1</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.62</v>
-      </c>
-      <c r="BC6">
-        <v>2.75</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45842.5</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45842</v>
       </c>
       <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
         <v>58</v>
       </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L7">
-        <v>3.77</v>
+        <v>4.05</v>
       </c>
       <c r="M7">
-        <v>3.37</v>
+        <v>3.7</v>
       </c>
       <c r="N7">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="O7">
         <v>2.45</v>
@@ -1903,49 +1636,49 @@
         <v>1.62</v>
       </c>
       <c r="R7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T7">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U7">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V7">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y7">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AA7">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AB7">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AC7">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AD7">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="AE7">
         <v>1.36</v>
       </c>
       <c r="AF7">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AG7">
         <v>2</v>
@@ -1954,105 +1687,51 @@
         <v>5</v>
       </c>
       <c r="AI7">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ7" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="AK7" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL7">
-        <v>1.25</v>
-      </c>
-      <c r="AM7">
-        <v>1.25</v>
-      </c>
-      <c r="AN7">
-        <v>1.25</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>1.2</v>
-      </c>
-      <c r="AQ7">
-        <v>1.45</v>
-      </c>
-      <c r="AR7">
-        <v>1.73</v>
-      </c>
-      <c r="AS7">
-        <v>2.17</v>
-      </c>
-      <c r="AT7">
-        <v>2.83</v>
-      </c>
-      <c r="AU7">
-        <v>3.72</v>
-      </c>
-      <c r="AV7">
-        <v>2.64</v>
-      </c>
-      <c r="AW7">
-        <v>1.99</v>
-      </c>
-      <c r="AX7">
-        <v>1.58</v>
-      </c>
-      <c r="AY7">
-        <v>1.33</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>2.45</v>
-      </c>
-      <c r="BC7">
-        <v>1.62</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>153</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45842.5</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45842</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L8">
         <v>1.34</v>
@@ -2127,111 +1806,57 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="AK8" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>-1</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>0</v>
-      </c>
-      <c r="BC8">
-        <v>0</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45842.53125</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45842</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D9" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L9">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="M9">
-        <v>3.35</v>
+        <v>3.61</v>
       </c>
       <c r="N9">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="O9">
         <v>2.5</v>
@@ -2243,43 +1868,43 @@
         <v>1.57</v>
       </c>
       <c r="R9">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S9">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
         <v>2.37</v>
       </c>
       <c r="U9">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V9">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z9">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AA9">
         <v>4.3</v>
       </c>
       <c r="AB9">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AC9">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="AD9">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AE9">
         <v>1.42</v>
@@ -2288,7 +1913,7 @@
         <v>1.6</v>
       </c>
       <c r="AG9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH9">
         <v>5.05</v>
@@ -2297,102 +1922,48 @@
         <v>1.15</v>
       </c>
       <c r="AJ9" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK9" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL9">
-        <v>1.17</v>
-      </c>
-      <c r="AM9">
-        <v>1.26</v>
-      </c>
-      <c r="AN9">
-        <v>1.12</v>
-      </c>
-      <c r="AO9">
-        <v>-1</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>2.5</v>
-      </c>
-      <c r="BC9">
-        <v>1.57</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>154</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45842.54166666666</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45842</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L10">
         <v>1.82</v>
@@ -2467,87 +2038,33 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="AK10" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <v>-1</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>0</v>
-      </c>
-      <c r="BC10">
-        <v>0</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45842.62152777778</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45842</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2562,186 +2079,132 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L11">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="M11">
-        <v>3.03</v>
+        <v>3.2</v>
       </c>
       <c r="N11">
+        <v>2.73</v>
+      </c>
+      <c r="O11">
+        <v>1.8</v>
+      </c>
+      <c r="P11">
+        <v>8</v>
+      </c>
+      <c r="Q11">
+        <v>2.25</v>
+      </c>
+      <c r="R11">
+        <v>1.36</v>
+      </c>
+      <c r="S11">
         <v>2.55</v>
       </c>
-      <c r="O11">
-        <v>1.91</v>
-      </c>
-      <c r="P11">
-        <v>7.5</v>
-      </c>
-      <c r="Q11">
-        <v>2.1</v>
-      </c>
-      <c r="R11">
-        <v>1.44</v>
-      </c>
-      <c r="S11">
-        <v>2.6</v>
-      </c>
       <c r="T11">
-        <v>3.13</v>
+        <v>2.84</v>
       </c>
       <c r="U11">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V11">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="Z11">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AA11">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AB11">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC11">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AD11">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="AE11">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF11">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG11">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AH11">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="AI11">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AJ11" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK11" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL11">
-        <v>1.34</v>
-      </c>
-      <c r="AM11">
-        <v>1.3</v>
-      </c>
-      <c r="AN11">
-        <v>1.47</v>
-      </c>
-      <c r="AO11">
-        <v>-1</v>
-      </c>
-      <c r="AP11">
-        <v>1.29</v>
-      </c>
-      <c r="AQ11">
-        <v>1.48</v>
-      </c>
-      <c r="AR11">
-        <v>1.95</v>
-      </c>
-      <c r="AS11">
-        <v>2.18</v>
-      </c>
-      <c r="AT11">
-        <v>2.8</v>
-      </c>
-      <c r="AU11">
-        <v>3.3</v>
-      </c>
-      <c r="AV11">
-        <v>2.56</v>
-      </c>
-      <c r="AW11">
-        <v>1.99</v>
-      </c>
-      <c r="AX11">
-        <v>1.59</v>
-      </c>
-      <c r="AY11">
-        <v>1.38</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.91</v>
-      </c>
-      <c r="BC11">
-        <v>2.1</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45842</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L12">
         <v>4.6</v>
       </c>
       <c r="M12">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="N12">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="O12">
         <v>3</v>
@@ -2774,7 +2237,7 @@
         <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z12">
         <v>1.3</v>
@@ -2783,22 +2246,22 @@
         <v>3.2</v>
       </c>
       <c r="AB12">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AC12">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AD12">
         <v>3.25</v>
       </c>
       <c r="AE12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF12">
         <v>1.98</v>
       </c>
       <c r="AG12">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH12">
         <v>6.25</v>
@@ -2807,600 +2270,384 @@
         <v>1.1</v>
       </c>
       <c r="AJ12" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK12" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL12">
-        <v>1.24</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>1.17</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>1.33</v>
-      </c>
-      <c r="AQ12">
-        <v>1.57</v>
-      </c>
-      <c r="AR12">
-        <v>2.2</v>
-      </c>
-      <c r="AS12">
-        <v>2.4</v>
-      </c>
-      <c r="AT12">
-        <v>3.28</v>
-      </c>
-      <c r="AU12">
-        <v>3.14</v>
-      </c>
-      <c r="AV12">
-        <v>2.25</v>
-      </c>
-      <c r="AW12">
-        <v>1.75</v>
-      </c>
-      <c r="AX12">
-        <v>1.5</v>
-      </c>
-      <c r="AY12">
-        <v>1.25</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>3</v>
-      </c>
-      <c r="BC12">
-        <v>1.44</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>155</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45842</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E13" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L13">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="M13">
-        <v>3.7</v>
+        <v>5.01</v>
       </c>
       <c r="N13">
-        <v>5.3</v>
+        <v>7.38</v>
       </c>
       <c r="O13">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="P13">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R13">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S13">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="T13">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="U13">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V13">
-        <v>6.5</v>
+        <v>4.9</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Z13">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AA13">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AB13">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AC13">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AD13">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AE13">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AF13">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH13">
-        <v>7.17</v>
+        <v>4.93</v>
       </c>
       <c r="AI13">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AJ13" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="AK13" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL13">
-        <v>1.23</v>
-      </c>
-      <c r="AM13">
-        <v>1.2</v>
-      </c>
-      <c r="AN13">
-        <v>2.35</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>1.36</v>
-      </c>
-      <c r="AQ13">
-        <v>1.59</v>
-      </c>
-      <c r="AR13">
-        <v>1.86</v>
-      </c>
-      <c r="AS13">
-        <v>2.56</v>
-      </c>
-      <c r="AT13">
-        <v>3.34</v>
-      </c>
-      <c r="AU13">
-        <v>3.08</v>
-      </c>
-      <c r="AV13">
-        <v>2.29</v>
-      </c>
-      <c r="AW13">
-        <v>1.81</v>
-      </c>
-      <c r="AX13">
-        <v>1.48</v>
-      </c>
-      <c r="AY13">
-        <v>1.24</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.4</v>
-      </c>
-      <c r="BC13">
-        <v>3.4</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>156</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45842</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
         <v>128</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>147</v>
-      </c>
       <c r="L14">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="M14">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="N14">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="O14">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="P14">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="R14">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S14">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T14">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U14">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V14">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="W14">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Z14">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AA14">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AC14">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AD14">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AE14">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AF14">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AH14">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="AI14">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AJ14" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK14" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL14">
-        <v>1.24</v>
-      </c>
-      <c r="AM14">
-        <v>1.2</v>
-      </c>
-      <c r="AN14">
-        <v>2.3</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>1.3</v>
-      </c>
-      <c r="AQ14">
-        <v>1.46</v>
-      </c>
-      <c r="AR14">
-        <v>2.07</v>
-      </c>
-      <c r="AS14">
-        <v>2.32</v>
-      </c>
-      <c r="AT14">
-        <v>3.08</v>
-      </c>
-      <c r="AU14">
-        <v>3.42</v>
-      </c>
-      <c r="AV14">
-        <v>2.28</v>
-      </c>
-      <c r="AW14">
-        <v>1.94</v>
-      </c>
-      <c r="AX14">
-        <v>1.57</v>
-      </c>
-      <c r="AY14">
-        <v>1.28</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.4</v>
-      </c>
-      <c r="BC14">
-        <v>3.5</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45842</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E15" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F15" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L15">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="M15">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="N15">
-        <v>3.03</v>
+        <v>5.4</v>
       </c>
       <c r="O15">
+        <v>1.4</v>
+      </c>
+      <c r="P15">
+        <v>8.5</v>
+      </c>
+      <c r="Q15">
+        <v>3.5</v>
+      </c>
+      <c r="R15">
+        <v>1.36</v>
+      </c>
+      <c r="S15">
+        <v>2.8</v>
+      </c>
+      <c r="T15">
+        <v>2.75</v>
+      </c>
+      <c r="U15">
+        <v>1.36</v>
+      </c>
+      <c r="V15">
+        <v>6.2</v>
+      </c>
+      <c r="W15">
+        <v>1.08</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>8.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.3</v>
+      </c>
+      <c r="AA15">
+        <v>3.25</v>
+      </c>
+      <c r="AB15">
+        <v>2</v>
+      </c>
+      <c r="AC15">
         <v>1.8</v>
       </c>
-      <c r="P15">
-        <v>8</v>
-      </c>
-      <c r="Q15">
-        <v>2.25</v>
-      </c>
-      <c r="R15">
-        <v>1.42</v>
-      </c>
-      <c r="S15">
-        <v>2.55</v>
-      </c>
-      <c r="T15">
-        <v>3.04</v>
-      </c>
-      <c r="U15">
-        <v>1.33</v>
-      </c>
-      <c r="V15">
-        <v>8.25</v>
-      </c>
-      <c r="W15">
-        <v>1.06</v>
-      </c>
-      <c r="X15">
-        <v>1.05</v>
-      </c>
-      <c r="Y15">
-        <v>7.75</v>
-      </c>
-      <c r="Z15">
-        <v>1.33</v>
-      </c>
-      <c r="AA15">
-        <v>3</v>
-      </c>
-      <c r="AB15">
-        <v>2.05</v>
-      </c>
-      <c r="AC15">
-        <v>1.61</v>
-      </c>
       <c r="AD15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AE15">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AF15">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AG15">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AH15">
-        <v>7.8</v>
+        <v>6.75</v>
       </c>
       <c r="AI15">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AJ15" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="AK15" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL15">
-        <v>1.32</v>
-      </c>
-      <c r="AM15">
-        <v>1.28</v>
-      </c>
-      <c r="AN15">
-        <v>1.55</v>
-      </c>
-      <c r="AO15">
-        <v>-1</v>
-      </c>
-      <c r="AP15">
-        <v>1.25</v>
-      </c>
-      <c r="AQ15">
-        <v>1.42</v>
-      </c>
-      <c r="AR15">
-        <v>1.67</v>
-      </c>
-      <c r="AS15">
-        <v>2.12</v>
-      </c>
-      <c r="AT15">
-        <v>2.78</v>
-      </c>
-      <c r="AU15">
-        <v>3.82</v>
-      </c>
-      <c r="AV15">
-        <v>2.67</v>
-      </c>
-      <c r="AW15">
-        <v>2.09</v>
-      </c>
-      <c r="AX15">
-        <v>1.61</v>
-      </c>
-      <c r="AY15">
-        <v>1.34</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.8</v>
-      </c>
-      <c r="BC15">
-        <v>2.25</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>157</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45842</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -3412,508 +2659,346 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L16">
-        <v>1.38</v>
+        <v>2.62</v>
       </c>
       <c r="M16">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="N16">
-        <v>6.2</v>
+        <v>3.04</v>
       </c>
       <c r="O16">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="P16">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="Q16">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="R16">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="S16">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="T16">
-        <v>2.4</v>
+        <v>3.33</v>
       </c>
       <c r="U16">
-        <v>1.49</v>
+        <v>1.31</v>
       </c>
       <c r="V16">
-        <v>4.9</v>
+        <v>8.5</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y16">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="Z16">
+        <v>1.42</v>
+      </c>
+      <c r="AA16">
+        <v>2.7</v>
+      </c>
+      <c r="AB16">
+        <v>2.42</v>
+      </c>
+      <c r="AC16">
+        <v>1.61</v>
+      </c>
+      <c r="AD16">
+        <v>4.33</v>
+      </c>
+      <c r="AE16">
         <v>1.18</v>
       </c>
-      <c r="AA16">
-        <v>4.2</v>
-      </c>
-      <c r="AB16">
-        <v>1.6</v>
-      </c>
-      <c r="AC16">
-        <v>2.1</v>
-      </c>
-      <c r="AD16">
-        <v>2.55</v>
-      </c>
-      <c r="AE16">
-        <v>1.41</v>
-      </c>
       <c r="AF16">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG16">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AH16">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="AI16">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="AJ16" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="AK16" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL16">
-        <v>1.07</v>
-      </c>
-      <c r="AM16">
-        <v>1.15</v>
-      </c>
-      <c r="AN16">
-        <v>2.95</v>
-      </c>
-      <c r="AO16">
-        <v>-1</v>
-      </c>
-      <c r="AP16">
-        <v>1.31</v>
-      </c>
-      <c r="AQ16">
-        <v>1.58</v>
-      </c>
-      <c r="AR16">
-        <v>2.25</v>
-      </c>
-      <c r="AS16">
-        <v>2.62</v>
-      </c>
-      <c r="AT16">
-        <v>3.45</v>
-      </c>
-      <c r="AU16">
-        <v>2.92</v>
-      </c>
-      <c r="AV16">
-        <v>2.12</v>
-      </c>
-      <c r="AW16">
-        <v>1.78</v>
-      </c>
-      <c r="AX16">
-        <v>1.44</v>
-      </c>
-      <c r="AY16">
-        <v>1.22</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.3</v>
-      </c>
-      <c r="BC16">
-        <v>3.75</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45842</v>
       </c>
       <c r="B17" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F17" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L17">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="M17">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="N17">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="P17">
         <v>9</v>
       </c>
       <c r="Q17">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R17">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S17">
         <v>3.2</v>
       </c>
       <c r="T17">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
       <c r="U17">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="V17">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Z17">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AA17">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AB17">
-        <v>1.79</v>
+        <v>1.6</v>
       </c>
       <c r="AC17">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD17">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AE17">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH17">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AI17">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AJ17" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="AK17" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL17">
-        <v>1.29</v>
-      </c>
-      <c r="AM17">
-        <v>1.25</v>
-      </c>
-      <c r="AN17">
-        <v>1.72</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>1.31</v>
-      </c>
-      <c r="AQ17">
-        <v>1.62</v>
-      </c>
-      <c r="AR17">
-        <v>1.98</v>
-      </c>
-      <c r="AS17">
-        <v>2.59</v>
-      </c>
-      <c r="AT17">
-        <v>3.58</v>
-      </c>
-      <c r="AU17">
-        <v>2.97</v>
-      </c>
-      <c r="AV17">
-        <v>2.1</v>
-      </c>
-      <c r="AW17">
-        <v>1.72</v>
-      </c>
-      <c r="AX17">
-        <v>1.41</v>
-      </c>
-      <c r="AY17">
-        <v>1.21</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.67</v>
-      </c>
-      <c r="BC17">
-        <v>2.25</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45842</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="D18" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L18">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="M18">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="N18">
-        <v>2.74</v>
+        <v>5.5</v>
       </c>
       <c r="O18">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="P18">
+        <v>9.5</v>
+      </c>
+      <c r="Q18">
+        <v>3.4</v>
+      </c>
+      <c r="R18">
+        <v>1.36</v>
+      </c>
+      <c r="S18">
+        <v>2.7</v>
+      </c>
+      <c r="T18">
+        <v>3.06</v>
+      </c>
+      <c r="U18">
+        <v>1.36</v>
+      </c>
+      <c r="V18">
+        <v>6.2</v>
+      </c>
+      <c r="W18">
+        <v>1.07</v>
+      </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
         <v>8.5</v>
       </c>
-      <c r="Q18">
-        <v>2.2</v>
-      </c>
-      <c r="R18">
-        <v>1.4</v>
-      </c>
-      <c r="S18">
-        <v>2.8</v>
-      </c>
-      <c r="T18">
-        <v>2.8</v>
-      </c>
-      <c r="U18">
-        <v>1.4</v>
-      </c>
-      <c r="V18">
-        <v>7</v>
-      </c>
-      <c r="W18">
-        <v>1.08</v>
-      </c>
-      <c r="X18">
-        <v>1.01</v>
-      </c>
-      <c r="Y18">
-        <v>9.25</v>
-      </c>
       <c r="Z18">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AA18">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AC18">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AD18">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AE18">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AF18">
+        <v>2.11</v>
+      </c>
+      <c r="AG18">
         <v>1.7</v>
       </c>
-      <c r="AG18">
-        <v>2</v>
-      </c>
       <c r="AH18">
-        <v>6.82</v>
+        <v>7.18</v>
       </c>
       <c r="AI18">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AJ18" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="AK18" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL18">
-        <v>1.25</v>
-      </c>
-      <c r="AM18">
-        <v>1.25</v>
-      </c>
-      <c r="AN18">
-        <v>1.44</v>
-      </c>
-      <c r="AO18">
-        <v>-1</v>
-      </c>
-      <c r="AP18">
-        <v>1.35</v>
-      </c>
-      <c r="AQ18">
-        <v>1.68</v>
-      </c>
-      <c r="AR18">
-        <v>2.45</v>
-      </c>
-      <c r="AS18">
-        <v>2.73</v>
-      </c>
-      <c r="AT18">
-        <v>3.84</v>
-      </c>
-      <c r="AU18">
-        <v>2.81</v>
-      </c>
-      <c r="AV18">
-        <v>2.08</v>
-      </c>
-      <c r="AW18">
-        <v>1.66</v>
-      </c>
-      <c r="AX18">
-        <v>1.37</v>
-      </c>
-      <c r="AY18">
-        <v>1.25</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.73</v>
-      </c>
-      <c r="BC18">
-        <v>2.2</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>158</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45842</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
         <v>85</v>
       </c>
-      <c r="E19" t="s">
-        <v>103</v>
-      </c>
       <c r="F19" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -3922,186 +3007,132 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L19">
-        <v>1.79</v>
+        <v>2.45</v>
       </c>
       <c r="M19">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N19">
-        <v>3.63</v>
+        <v>2.61</v>
       </c>
       <c r="O19">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="P19">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
+        <v>1.4</v>
+      </c>
+      <c r="S19">
+        <v>2.7</v>
+      </c>
+      <c r="T19">
+        <v>2.8</v>
+      </c>
+      <c r="U19">
+        <v>1.38</v>
+      </c>
+      <c r="V19">
+        <v>7</v>
+      </c>
+      <c r="W19">
+        <v>1.08</v>
+      </c>
+      <c r="X19">
+        <v>1.01</v>
+      </c>
+      <c r="Y19">
+        <v>9.25</v>
+      </c>
+      <c r="Z19">
         <v>1.3</v>
       </c>
-      <c r="S19">
-        <v>3.2</v>
-      </c>
-      <c r="T19">
-        <v>2.37</v>
-      </c>
-      <c r="U19">
-        <v>1.5</v>
-      </c>
-      <c r="V19">
-        <v>5.75</v>
-      </c>
-      <c r="W19">
-        <v>1.12</v>
-      </c>
-      <c r="X19">
-        <v>1.03</v>
-      </c>
-      <c r="Y19">
-        <v>11.5</v>
-      </c>
-      <c r="Z19">
-        <v>1.17</v>
-      </c>
       <c r="AA19">
-        <v>4.2</v>
+        <v>3.08</v>
       </c>
       <c r="AB19">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AC19">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AD19">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AE19">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AF19">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AH19">
-        <v>4.7</v>
+        <v>6.82</v>
       </c>
       <c r="AI19">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AJ19" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="AK19" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL19">
-        <v>1.25</v>
-      </c>
-      <c r="AM19">
-        <v>1.22</v>
-      </c>
-      <c r="AN19">
-        <v>1.75</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>1.3</v>
-      </c>
-      <c r="AQ19">
-        <v>1.59</v>
-      </c>
-      <c r="AR19">
-        <v>2.3</v>
-      </c>
-      <c r="AS19">
-        <v>2.46</v>
-      </c>
-      <c r="AT19">
-        <v>3.56</v>
-      </c>
-      <c r="AU19">
-        <v>2.99</v>
-      </c>
-      <c r="AV19">
-        <v>2.19</v>
-      </c>
-      <c r="AW19">
-        <v>1.73</v>
-      </c>
-      <c r="AX19">
-        <v>1.45</v>
-      </c>
-      <c r="AY19">
-        <v>1.21</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1.57</v>
-      </c>
-      <c r="BC19">
-        <v>2.5</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>159</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45842.65625</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45842</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K20" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L20">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="M20">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="N20">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O20">
         <v>0</v>
@@ -4143,10 +3174,10 @@
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC20">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AD20">
         <v>0</v>
@@ -4167,111 +3198,57 @@
         <v>0</v>
       </c>
       <c r="AJ20" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="AK20" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>0</v>
-      </c>
-      <c r="AO20">
-        <v>-1</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>0</v>
-      </c>
-      <c r="BC20">
-        <v>0</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45842.77083333334</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45842</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F21" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L21">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M21">
-        <v>3.12</v>
+        <v>3.32</v>
       </c>
       <c r="N21">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="O21">
         <v>1.61</v>
@@ -4286,37 +3263,37 @@
         <v>1.61</v>
       </c>
       <c r="S21">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U21">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="V21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="W21">
         <v>1.03</v>
       </c>
       <c r="X21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y21">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z21">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AA21">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB21">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="AC21">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AD21">
         <v>5.5</v>
@@ -4325,102 +3302,48 @@
         <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AG21">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH21">
-        <v>15</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI21">
         <v>1</v>
       </c>
       <c r="AJ21" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AK21" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL21">
-        <v>1.28</v>
-      </c>
-      <c r="AM21">
-        <v>1.35</v>
-      </c>
-      <c r="AN21">
-        <v>2.2</v>
-      </c>
-      <c r="AO21">
-        <v>-1</v>
-      </c>
-      <c r="AP21">
-        <v>1.23</v>
-      </c>
-      <c r="AQ21">
-        <v>1.28</v>
-      </c>
-      <c r="AR21">
-        <v>1.53</v>
-      </c>
-      <c r="AS21">
-        <v>1.85</v>
-      </c>
-      <c r="AT21">
-        <v>2.48</v>
-      </c>
-      <c r="AU21">
-        <v>3.8</v>
-      </c>
-      <c r="AV21">
-        <v>2.8</v>
-      </c>
-      <c r="AW21">
-        <v>2.3</v>
-      </c>
-      <c r="AX21">
-        <v>1.85</v>
-      </c>
-      <c r="AY21">
-        <v>1.51</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1.61</v>
-      </c>
-      <c r="BC21">
-        <v>3.25</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45842.79166666666</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45842</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E22" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F22" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -4432,16 +3355,16 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L22">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="M22">
-        <v>3.11</v>
+        <v>3.25</v>
       </c>
       <c r="N22">
-        <v>3.38</v>
+        <v>4.2</v>
       </c>
       <c r="O22">
         <v>1.8</v>
@@ -4453,19 +3376,19 @@
         <v>2.1</v>
       </c>
       <c r="R22">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S22">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="T22">
         <v>3.1</v>
       </c>
       <c r="U22">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -4474,144 +3397,90 @@
         <v>1.03</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AA22">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AB22">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC22">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AD22">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AE22">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AF22">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AG22">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH22">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AI22">
         <v>1.07</v>
       </c>
       <c r="AJ22" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AK22" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL22">
-        <v>1.32</v>
-      </c>
-      <c r="AM22">
-        <v>1.27</v>
-      </c>
-      <c r="AN22">
-        <v>1.7</v>
-      </c>
-      <c r="AO22">
-        <v>-1</v>
-      </c>
-      <c r="AP22">
-        <v>1.44</v>
-      </c>
-      <c r="AQ22">
-        <v>2</v>
-      </c>
-      <c r="AR22">
-        <v>2.27</v>
-      </c>
-      <c r="AS22">
-        <v>3.54</v>
-      </c>
-      <c r="AT22">
-        <v>5.35</v>
-      </c>
-      <c r="AU22">
-        <v>2.43</v>
-      </c>
-      <c r="AV22">
-        <v>1.89</v>
-      </c>
-      <c r="AW22">
-        <v>1.51</v>
-      </c>
-      <c r="AX22">
-        <v>1.21</v>
-      </c>
-      <c r="AY22">
-        <v>1.07</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1.8</v>
-      </c>
-      <c r="BC22">
-        <v>2.1</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45842.83333333334</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45842</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F23" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L23">
         <v>1.44</v>
       </c>
       <c r="M23">
-        <v>5.01</v>
+        <v>4.5</v>
       </c>
       <c r="N23">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="O23">
         <v>1.36</v>
@@ -4629,22 +3498,22 @@
         <v>3.6</v>
       </c>
       <c r="T23">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="U23">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="V23">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z23">
         <v>1.09</v>
@@ -4653,135 +3522,81 @@
         <v>5</v>
       </c>
       <c r="AB23">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC23">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="AD23">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AE23">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="AF23">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AG23">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AH23">
         <v>2.66</v>
       </c>
       <c r="AI23">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AJ23" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AK23" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL23">
-        <v>1.17</v>
-      </c>
-      <c r="AM23">
-        <v>1.12</v>
-      </c>
-      <c r="AN23">
-        <v>2.5</v>
-      </c>
-      <c r="AO23">
-        <v>-1</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>1.36</v>
-      </c>
-      <c r="BC23">
-        <v>3</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>161</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45842.85416666666</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45842</v>
       </c>
       <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
         <v>67</v>
       </c>
-      <c r="C24" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" t="s">
-        <v>85</v>
-      </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L24">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="M24">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="N24">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="O24">
         <v>1.57</v>
@@ -4793,19 +3608,19 @@
         <v>2.4</v>
       </c>
       <c r="R24">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S24">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="T24">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="U24">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="V24">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="W24">
         <v>1.16</v>
@@ -4817,132 +3632,78 @@
         <v>12</v>
       </c>
       <c r="Z24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AA24">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AB24">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC24">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="AD24">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AE24">
-        <v>1.62</v>
+        <v>1.85</v>
       </c>
       <c r="AF24">
         <v>1.5</v>
       </c>
       <c r="AG24">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AH24">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AI24">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AJ24" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AK24" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL24">
-        <v>1.13</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>2.3</v>
-      </c>
-      <c r="AO24">
-        <v>-1</v>
-      </c>
-      <c r="AP24">
-        <v>0</v>
-      </c>
-      <c r="AQ24">
-        <v>0</v>
-      </c>
-      <c r="AR24">
-        <v>0</v>
-      </c>
-      <c r="AS24">
-        <v>0</v>
-      </c>
-      <c r="AT24">
-        <v>0</v>
-      </c>
-      <c r="AU24">
-        <v>0</v>
-      </c>
-      <c r="AV24">
-        <v>0</v>
-      </c>
-      <c r="AW24">
-        <v>0</v>
-      </c>
-      <c r="AX24">
-        <v>0</v>
-      </c>
-      <c r="AY24">
-        <v>0</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>1.57</v>
-      </c>
-      <c r="BC24">
-        <v>2.4</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>162</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45842.89583333334</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45842</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F25" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I25">
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L25">
         <v>2.52</v>
@@ -5017,111 +3778,57 @@
         <v>1.19</v>
       </c>
       <c r="AJ25" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL25">
-        <v>1.52</v>
-      </c>
-      <c r="AM25">
-        <v>1.27</v>
-      </c>
-      <c r="AN25">
-        <v>1.47</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>1.3</v>
-      </c>
-      <c r="AQ25">
-        <v>1.53</v>
-      </c>
-      <c r="AR25">
-        <v>1.86</v>
-      </c>
-      <c r="AS25">
-        <v>2.33</v>
-      </c>
-      <c r="AT25">
-        <v>3</v>
-      </c>
-      <c r="AU25">
-        <v>3.15</v>
-      </c>
-      <c r="AV25">
-        <v>2.32</v>
-      </c>
-      <c r="AW25">
-        <v>1.82</v>
-      </c>
-      <c r="AX25">
-        <v>1.52</v>
-      </c>
-      <c r="AY25">
-        <v>1.32</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>2.05</v>
-      </c>
-      <c r="BC25">
-        <v>1.8</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>163</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45842.90625</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45842</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F26" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I26">
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L26">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="M26">
-        <v>3.39</v>
+        <v>3.4</v>
       </c>
       <c r="N26">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="O26">
         <v>0</v>
@@ -5133,165 +3840,111 @@
         <v>0</v>
       </c>
       <c r="R26">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S26">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="T26">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U26">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V26">
         <v>6</v>
       </c>
       <c r="W26">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AA26">
         <v>3.3</v>
       </c>
       <c r="AB26">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AC26">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AD26">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AE26">
         <v>1.32</v>
       </c>
       <c r="AF26">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AG26">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="AH26">
-        <v>5.95</v>
+        <v>5.6</v>
       </c>
       <c r="AI26">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AJ26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AK26" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL26">
-        <v>1.26</v>
-      </c>
-      <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>1.73</v>
-      </c>
-      <c r="AO26">
-        <v>-1</v>
-      </c>
-      <c r="AP26">
-        <v>1.23</v>
-      </c>
-      <c r="AQ26">
-        <v>1.63</v>
-      </c>
-      <c r="AR26">
-        <v>2.36</v>
-      </c>
-      <c r="AS26">
-        <v>2.31</v>
-      </c>
-      <c r="AT26">
-        <v>3.1</v>
-      </c>
-      <c r="AU26">
-        <v>3.38</v>
-      </c>
-      <c r="AV26">
-        <v>2.08</v>
-      </c>
-      <c r="AW26">
-        <v>1.92</v>
-      </c>
-      <c r="AX26">
-        <v>1.52</v>
-      </c>
-      <c r="AY26">
-        <v>1.28</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>0</v>
-      </c>
-      <c r="BC26">
-        <v>0</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>164</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45842.91666666666</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45842</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F27" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27">
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L27">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="M27">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="N27">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O27">
         <v>2.6</v>
@@ -5306,28 +3959,28 @@
         <v>1.32</v>
       </c>
       <c r="S27">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="T27">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U27">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V27">
         <v>7</v>
       </c>
       <c r="W27">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z27">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AA27">
         <v>3.7</v>
@@ -5336,123 +3989,69 @@
         <v>1.77</v>
       </c>
       <c r="AC27">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AD27">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE27">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF27">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG27">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH27">
         <v>5.5</v>
       </c>
       <c r="AI27">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AJ27" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK27" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL27">
-        <v>1.25</v>
-      </c>
-      <c r="AM27">
-        <v>1.25</v>
-      </c>
-      <c r="AN27">
-        <v>1.3</v>
-      </c>
-      <c r="AO27">
-        <v>-1</v>
-      </c>
-      <c r="AP27">
-        <v>1.36</v>
-      </c>
-      <c r="AQ27">
-        <v>1.68</v>
-      </c>
-      <c r="AR27">
-        <v>2.49</v>
-      </c>
-      <c r="AS27">
-        <v>2.78</v>
-      </c>
-      <c r="AT27">
-        <v>3.92</v>
-      </c>
-      <c r="AU27">
-        <v>2.76</v>
-      </c>
-      <c r="AV27">
-        <v>2.06</v>
-      </c>
-      <c r="AW27">
-        <v>1.69</v>
-      </c>
-      <c r="AX27">
-        <v>1.36</v>
-      </c>
-      <c r="AY27">
-        <v>1.17</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>2.6</v>
-      </c>
-      <c r="BC27">
-        <v>1.53</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>165</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45842.91666666666</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45842</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I28">
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L28">
         <v>1.82</v>
@@ -5530,108 +4129,54 @@
         <v>148</v>
       </c>
       <c r="AK28" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL28">
-        <v>1.29</v>
-      </c>
-      <c r="AM28">
-        <v>1.24</v>
-      </c>
-      <c r="AN28">
-        <v>1.87</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>1.28</v>
-      </c>
-      <c r="AQ28">
-        <v>1.49</v>
-      </c>
-      <c r="AR28">
-        <v>1.79</v>
-      </c>
-      <c r="AS28">
-        <v>2.23</v>
-      </c>
-      <c r="AT28">
-        <v>2.9</v>
-      </c>
-      <c r="AU28">
-        <v>3.2</v>
-      </c>
-      <c r="AV28">
-        <v>2.4</v>
-      </c>
-      <c r="AW28">
-        <v>1.9</v>
-      </c>
-      <c r="AX28">
-        <v>1.56</v>
-      </c>
-      <c r="AY28">
-        <v>1.35</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>1.57</v>
-      </c>
-      <c r="BC28">
-        <v>2.4</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>166</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45842.9375</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45842</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C29" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E29" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F29" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L29">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="M29">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N29">
-        <v>3.36</v>
+        <v>3.75</v>
       </c>
       <c r="O29">
         <v>1.53</v>
@@ -5643,16 +4188,16 @@
         <v>2.5</v>
       </c>
       <c r="R29">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S29">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="T29">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="V29">
         <v>6.75</v>
@@ -5661,129 +4206,75 @@
         <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y29">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Z29">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AA29">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AC29">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD29">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AE29">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG29">
         <v>1.85</v>
       </c>
       <c r="AH29">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="AI29">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AJ29" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK29" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL29">
-        <v>1.25</v>
-      </c>
-      <c r="AM29">
-        <v>1.24</v>
-      </c>
-      <c r="AN29">
-        <v>1.77</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>1.28</v>
-      </c>
-      <c r="AQ29">
-        <v>1.57</v>
-      </c>
-      <c r="AR29">
-        <v>1.96</v>
-      </c>
-      <c r="AS29">
-        <v>2.49</v>
-      </c>
-      <c r="AT29">
-        <v>3.4</v>
-      </c>
-      <c r="AU29">
-        <v>3.1</v>
-      </c>
-      <c r="AV29">
-        <v>2.17</v>
-      </c>
-      <c r="AW29">
-        <v>1.72</v>
-      </c>
-      <c r="AX29">
-        <v>1.45</v>
-      </c>
-      <c r="AY29">
-        <v>1.23</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.53</v>
-      </c>
-      <c r="BC29">
-        <v>2.5</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>167</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45842.97916666666</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45842</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C30" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E30" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F30" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5792,311 +4283,203 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L30">
-        <v>2.44</v>
+        <v>3.47</v>
       </c>
       <c r="M30">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="N30">
-        <v>2.47</v>
+        <v>2.11</v>
       </c>
       <c r="O30">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="P30">
-        <v>11</v>
+        <v>15.75</v>
       </c>
       <c r="Q30">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="R30">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S30">
-        <v>3.4</v>
+        <v>2.62</v>
       </c>
       <c r="T30">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>11</v>
+        <v>9.1</v>
       </c>
       <c r="Z30">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AA30">
-        <v>4</v>
+        <v>2.91</v>
       </c>
       <c r="AB30">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AC30">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="AD30">
-        <v>2.15</v>
+        <v>3.7</v>
       </c>
       <c r="AE30">
-        <v>1.61</v>
+        <v>1.19</v>
       </c>
       <c r="AF30">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>2.38</v>
+        <v>1.91</v>
       </c>
       <c r="AH30">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AI30">
-        <v>1.17</v>
+        <v>1.07</v>
       </c>
       <c r="AJ30" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="AK30" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL30">
-        <v>1.47</v>
-      </c>
-      <c r="AM30">
-        <v>1.28</v>
-      </c>
-      <c r="AN30">
-        <v>1.49</v>
-      </c>
-      <c r="AO30">
-        <v>-1</v>
-      </c>
-      <c r="AP30">
-        <v>1.21</v>
-      </c>
-      <c r="AQ30">
-        <v>1.38</v>
-      </c>
-      <c r="AR30">
-        <v>1.63</v>
-      </c>
-      <c r="AS30">
-        <v>1.98</v>
-      </c>
-      <c r="AT30">
-        <v>2.48</v>
-      </c>
-      <c r="AU30">
-        <v>3.8</v>
-      </c>
-      <c r="AV30">
-        <v>2.75</v>
-      </c>
-      <c r="AW30">
-        <v>2.12</v>
-      </c>
-      <c r="AX30">
-        <v>1.72</v>
-      </c>
-      <c r="AY30">
-        <v>1.47</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>2.05</v>
-      </c>
-      <c r="BC30">
-        <v>1.8</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>168</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45842.97916666666</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45842</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F31" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="L31">
-        <v>3.29</v>
+        <v>2.44</v>
       </c>
       <c r="M31">
-        <v>3.39</v>
+        <v>3.27</v>
       </c>
       <c r="N31">
-        <v>2</v>
+        <v>2.47</v>
       </c>
       <c r="O31">
+        <v>2.05</v>
+      </c>
+      <c r="P31">
+        <v>11</v>
+      </c>
+      <c r="Q31">
+        <v>1.8</v>
+      </c>
+      <c r="R31">
+        <v>1.3</v>
+      </c>
+      <c r="S31">
+        <v>3.4</v>
+      </c>
+      <c r="T31">
         <v>2.5</v>
       </c>
-      <c r="P31">
-        <v>15.75</v>
-      </c>
-      <c r="Q31">
-        <v>1.53</v>
-      </c>
-      <c r="R31">
-        <v>1.36</v>
-      </c>
-      <c r="S31">
-        <v>2.8</v>
-      </c>
-      <c r="T31">
-        <v>2.55</v>
-      </c>
       <c r="U31">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="V31">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="W31">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X31">
         <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="Z31">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AA31">
-        <v>3.11</v>
+        <v>4</v>
       </c>
       <c r="AB31">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AC31">
-        <v>1.83</v>
+        <v>2.08</v>
       </c>
       <c r="AD31">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="AE31">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
       <c r="AF31">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AG31">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AH31">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
       <c r="AI31">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AJ31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AK31" t="s">
-        <v>148</v>
-      </c>
-      <c r="AL31">
-        <v>1.28</v>
-      </c>
-      <c r="AM31">
-        <v>1.22</v>
-      </c>
-      <c r="AN31">
-        <v>1.24</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>1.48</v>
-      </c>
-      <c r="AQ31">
-        <v>1.72</v>
-      </c>
-      <c r="AR31">
-        <v>2.94</v>
-      </c>
-      <c r="AS31">
-        <v>3.28</v>
-      </c>
-      <c r="AT31">
-        <v>4.84</v>
-      </c>
-      <c r="AU31">
-        <v>2.41</v>
-      </c>
-      <c r="AV31">
-        <v>1.9</v>
-      </c>
-      <c r="AW31">
-        <v>1.49</v>
-      </c>
-      <c r="AX31">
-        <v>1.25</v>
-      </c>
-      <c r="AY31">
-        <v>1.1</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>2.5</v>
-      </c>
-      <c r="BC31">
-        <v>1.53</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>129</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45842.97916666666</v>
       </c>
     </row>

--- a/jogos_2025-07-04.xlsx
+++ b/jogos_2025-07-04.xlsx
@@ -781,30 +781,30 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -837,16 +837,16 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -856,12 +856,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '53', '87', '9003']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.05</v>
-      </c>
       <c r="W4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X4" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AB4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['36', '41']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['47']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AC4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>['78', '4']</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['65', '52']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45842.5</v>
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>4.83</v>
+        <v>3.1</v>
       </c>
       <c r="N5" t="n">
-        <v>6.83</v>
+        <v>3.37</v>
       </c>
       <c r="O5" t="n">
-        <v>1.85</v>
+        <v>2.74</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.8</v>
+        <v>3.8</v>
       </c>
       <c r="R5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
         <v>1.33</v>
       </c>
-      <c r="S5" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.18</v>
       </c>
-      <c r="X5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC5" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['36', '41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45842.5</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,22 +1288,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>4.05</v>
       </c>
       <c r="M7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.1</v>
       </c>
-      <c r="N7" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.6</v>
-      </c>
       <c r="T7" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['78', '4']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['65', '52']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.3</v>
       </c>
-      <c r="V7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.62</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45842.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>4.95</v>
+        <v>4.3</v>
       </c>
       <c r="N9" t="n">
-        <v>8</v>
+        <v>5.37</v>
       </c>
       <c r="O9" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="P9" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.75</v>
+        <v>5.92</v>
       </c>
       <c r="R9" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S9" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="V9" t="n">
         <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.55</v>
+        <v>1.98</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.28</v>
+        <v>2.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['45', '63']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45842.54166666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="M10" t="n">
-        <v>4.3</v>
+        <v>4.95</v>
       </c>
       <c r="N10" t="n">
-        <v>5.37</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.05</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U10" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="V10" t="n">
         <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X10" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.98</v>
+        <v>2.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['45', '63']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AJ10" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45842.54166666666</v>
@@ -1942,94 +1942,94 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
+          <t>['4', '90']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.15</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>['20', '60', '90+3', '90+4']</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI13" t="n">
         <v>3</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45842.65625</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.06</v>
+        <v>2.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.78</v>
+        <v>1.94</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.7</v>
+        <v>2.15</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['24', '5', '41', '36', '52', '57', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>['49', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45842.65625</v>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.73</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.9</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>6.7</v>
       </c>
       <c r="R15" t="n">
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="n">
         <v>1.8</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '6', '83']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45842.65625</v>
@@ -2578,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2604,65 +2604,65 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>3.04</v>
+        <v>2.73</v>
       </c>
       <c r="O17" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="T17" t="n">
-        <v>3.33</v>
+        <v>2.84</v>
       </c>
       <c r="U17" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W17" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="X17" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45842.65625</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>1.55</v>
+        <v>3.04</v>
       </c>
       <c r="O18" t="n">
-        <v>4.8</v>
+        <v>3.05</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.75</v>
+        <v>3.33</v>
       </c>
       <c r="U18" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
         <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="X18" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.07</v>
+        <v>2.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AA18" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
+          <t>['50']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['20', '60', '90+3', '90+4']</t>
-        </is>
-      </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.15</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45842.65625</v>
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.33</v>
+        <v>2.45</v>
       </c>
       <c r="M19" t="n">
-        <v>5.01</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>7.38</v>
+        <v>2.61</v>
       </c>
       <c r="O19" t="n">
-        <v>1.85</v>
+        <v>2.95</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.3</v>
       </c>
-      <c r="S19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="X19" t="n">
-        <v>4.33</v>
+        <v>3.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['5', '30']</t>
+          <t>['85']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['81']</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45842.65625</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2.45</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="AB20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['5', '30']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI20" t="n">
         <v>1.3</v>
       </c>
-      <c r="X20" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['85']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['53']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AJ20" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45842.65625</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="P21" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="R21" t="n">
         <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T21" t="n">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="U21" t="n">
         <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="W21" t="n">
         <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AA21" t="n">
         <v>3.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['2', '6', '83']</t>
+          <t>['24', '5', '41', '36', '52', '57', '73']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['49', '79']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AI21" t="n">
         <v>1.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45842.65625</v>
@@ -4126,19 +4126,19 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -4152,83 +4152,83 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.04</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.25</v>
+        <v>2.26</v>
       </c>
       <c r="O29" t="n">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>2.86</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S29" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['9']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.25</v>
       </c>
-      <c r="X29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['67']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>['11', '83']</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH29" t="n">
+      <c r="AI29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45842.91666666666</v>
@@ -4255,19 +4255,19 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>2.04</v>
       </c>
       <c r="M30" t="n">
         <v>3.4</v>
       </c>
       <c r="N30" t="n">
-        <v>2.26</v>
+        <v>3.25</v>
       </c>
       <c r="O30" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X30" t="n">
         <v>3.3</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="Y30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.32</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['11', '83']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45842.91666666666</v>
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="M33" t="n">
-        <v>3.27</v>
+        <v>3.52</v>
       </c>
       <c r="N33" t="n">
-        <v>2.47</v>
+        <v>3.05</v>
       </c>
       <c r="O33" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="P33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
       </c>
       <c r="U33" t="n">
         <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W33" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.15</v>
+        <v>2.72</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,16 +4735,16 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="AI33" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45842.97916666666</v>
